--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_healthcare_support_services.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_healthcare_support_services.xlsx
@@ -1127,43 +1127,43 @@
         <v>3.77931034482759</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>98.93151268778109</v>
       </c>
       <c r="G2">
         <v>6.84636118598383</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.198652291105121</v>
       </c>
       <c r="I2">
         <v>0.344640434192673</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>48.3</v>
       </c>
       <c r="L2">
-        <v>78.09839924021</v>
+        <v>77.30866084915441</v>
       </c>
       <c r="M2">
         <v>45.2</v>
       </c>
       <c r="N2">
-        <v>49.59839924021</v>
+        <v>49.5456608491544</v>
       </c>
       <c r="O2">
         <v>25.4</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.737</v>
       </c>
       <c r="Q2">
         <v>0.0921895851091542</v>
       </c>
       <c r="R2">
-        <v>0.088075744359787</v>
+        <v>0.08812074435978701</v>
       </c>
       <c r="S2">
         <v>0.0577366166625341</v>
@@ -1185,13 +1185,13 @@
         <v>0.110307709302615</v>
       </c>
       <c r="X2">
-        <v>0.088075744359787</v>
+        <v>0.0885027720805929</v>
       </c>
       <c r="Y2">
         <v>1.25737532244415</v>
       </c>
       <c r="Z2">
-        <v>0.824032945373846</v>
+        <v>0.832356510478632</v>
       </c>
       <c r="AA2">
         <v>25.4</v>
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08807574435978699</v>
+        <v>0.08812074435978701</v>
       </c>
       <c r="C2">
-        <v>78.09839924021</v>
+        <v>77.30866084915442</v>
       </c>
       <c r="D2">
-        <v>49.59839924021</v>
+        <v>49.54566084915441</v>
       </c>
       <c r="E2">
-        <v>-25.4</v>
+        <v>-24.663</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.7369999999999999</v>
       </c>
       <c r="G2">
         <v>28.5</v>
@@ -1445,28 +1445,28 @@
         <v>3.6675</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.03707109999999999</v>
       </c>
       <c r="N2">
-        <v>3.6675</v>
+        <v>3.6304289</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>3.6675</v>
+        <v>3.6304289</v>
       </c>
       <c r="Q2">
-        <v>4.637499999999999</v>
+        <v>4.600428899999999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08807574435978699</v>
+        <v>0.08850277208059293</v>
       </c>
       <c r="T2">
-        <v>0.8240329453738456</v>
+        <v>0.832356510478632</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>98.93151268778107</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08812074435978701</v>
+        <v>0.08816574435978697</v>
       </c>
       <c r="C3">
-        <v>77.30866084915442</v>
+        <v>76.51903449331191</v>
       </c>
       <c r="D3">
-        <v>49.54566084915441</v>
+        <v>49.49303449331192</v>
       </c>
       <c r="E3">
-        <v>-24.663</v>
+        <v>-23.926</v>
       </c>
       <c r="F3">
-        <v>0.7369999999999999</v>
+        <v>1.474</v>
       </c>
       <c r="G3">
         <v>28.5</v>
@@ -1527,28 +1527,28 @@
         <v>3.6675</v>
       </c>
       <c r="M3">
-        <v>0.03707109999999999</v>
+        <v>0.07414219999999998</v>
       </c>
       <c r="N3">
-        <v>3.6304289</v>
+        <v>3.5933578</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>3.6304289</v>
+        <v>3.5933578</v>
       </c>
       <c r="Q3">
-        <v>4.600428899999999</v>
+        <v>4.563357799999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08850277208059293</v>
+        <v>0.08893851465284386</v>
       </c>
       <c r="T3">
-        <v>0.832356510478632</v>
+        <v>0.8408499442590261</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>98.93151268778107</v>
+        <v>49.46575634389053</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08816574435978697</v>
+        <v>0.08821074435978699</v>
       </c>
       <c r="C4">
-        <v>76.51903449331191</v>
+        <v>75.72951981605689</v>
       </c>
       <c r="D4">
-        <v>49.49303449331192</v>
+        <v>49.44051981605689</v>
       </c>
       <c r="E4">
-        <v>-23.926</v>
+        <v>-23.189</v>
       </c>
       <c r="F4">
-        <v>1.474</v>
+        <v>2.210999999999999</v>
       </c>
       <c r="G4">
         <v>28.5</v>
@@ -1609,28 +1609,28 @@
         <v>3.6675</v>
       </c>
       <c r="M4">
-        <v>0.07414219999999998</v>
+        <v>0.1112133</v>
       </c>
       <c r="N4">
-        <v>3.5933578</v>
+        <v>3.556286699999999</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>3.5933578</v>
+        <v>3.556286699999999</v>
       </c>
       <c r="Q4">
-        <v>4.563357799999999</v>
+        <v>4.526286699999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08893851465284386</v>
+        <v>0.08938324160802782</v>
       </c>
       <c r="T4">
-        <v>0.8408499442590261</v>
+        <v>0.8495185003854078</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>49.46575634389053</v>
+        <v>32.97717089592702</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08821074435978699</v>
+        <v>0.08825574435978699</v>
       </c>
       <c r="C5">
-        <v>75.72951981605689</v>
+        <v>74.94011646227587</v>
       </c>
       <c r="D5">
-        <v>49.44051981605689</v>
+        <v>49.38811646227586</v>
       </c>
       <c r="E5">
-        <v>-23.189</v>
+        <v>-22.452</v>
       </c>
       <c r="F5">
-        <v>2.210999999999999</v>
+        <v>2.948</v>
       </c>
       <c r="G5">
         <v>28.5</v>
@@ -1691,28 +1691,28 @@
         <v>3.6675</v>
       </c>
       <c r="M5">
-        <v>0.1112133</v>
+        <v>0.1482844</v>
       </c>
       <c r="N5">
-        <v>3.556286699999999</v>
+        <v>3.519215599999999</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>3.556286699999999</v>
+        <v>3.519215599999999</v>
       </c>
       <c r="Q5">
-        <v>4.526286699999999</v>
+        <v>4.4892156</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08938324160802782</v>
+        <v>0.08983723370811145</v>
       </c>
       <c r="T5">
-        <v>0.8495185003854078</v>
+        <v>0.8583676514310893</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>32.97717089592702</v>
+        <v>24.73287817194527</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08825574435978699</v>
+        <v>0.08830074435978699</v>
       </c>
       <c r="C6">
-        <v>74.94011646227587</v>
+        <v>74.15082407835928</v>
       </c>
       <c r="D6">
-        <v>49.38811646227586</v>
+        <v>49.33582407835928</v>
       </c>
       <c r="E6">
-        <v>-22.452</v>
+        <v>-21.715</v>
       </c>
       <c r="F6">
-        <v>2.948</v>
+        <v>3.685</v>
       </c>
       <c r="G6">
         <v>28.5</v>
@@ -1773,28 +1773,28 @@
         <v>3.6675</v>
       </c>
       <c r="M6">
-        <v>0.1482844</v>
+        <v>0.1853555</v>
       </c>
       <c r="N6">
-        <v>3.519215599999999</v>
+        <v>3.4821445</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>3.519215599999999</v>
+        <v>3.4821445</v>
       </c>
       <c r="Q6">
-        <v>4.4892156</v>
+        <v>4.452144499999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08983723370811145</v>
+        <v>0.09030078353661788</v>
       </c>
       <c r="T6">
-        <v>0.8583676514310893</v>
+        <v>0.8674031003935216</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>24.73287817194527</v>
+        <v>19.78630253755621</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08830074435978699</v>
+        <v>0.088345744359787</v>
       </c>
       <c r="C7">
-        <v>74.15082407835928</v>
+        <v>73.36164231219362</v>
       </c>
       <c r="D7">
-        <v>49.33582407835928</v>
+        <v>49.28364231219361</v>
       </c>
       <c r="E7">
-        <v>-21.715</v>
+        <v>-20.978</v>
       </c>
       <c r="F7">
-        <v>3.685</v>
+        <v>4.422</v>
       </c>
       <c r="G7">
         <v>28.5</v>
@@ -1855,28 +1855,28 @@
         <v>3.6675</v>
       </c>
       <c r="M7">
-        <v>0.1853555</v>
+        <v>0.2224266</v>
       </c>
       <c r="N7">
-        <v>3.4821445</v>
+        <v>3.4450734</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>3.4821445</v>
+        <v>3.4450734</v>
       </c>
       <c r="Q7">
-        <v>4.452144499999999</v>
+        <v>4.415073399999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09030078353661788</v>
+        <v>0.09077419612743297</v>
       </c>
       <c r="T7">
-        <v>0.8674031003935216</v>
+        <v>0.8766307929508996</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>19.78630253755621</v>
+        <v>16.48858544796351</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08834574435978698</v>
+        <v>0.088390744359787</v>
       </c>
       <c r="C8">
-        <v>73.36164231219364</v>
+        <v>72.5725708131535</v>
       </c>
       <c r="D8">
-        <v>49.28364231219363</v>
+        <v>49.2315708131535</v>
       </c>
       <c r="E8">
-        <v>-20.978</v>
+        <v>-20.241</v>
       </c>
       <c r="F8">
-        <v>4.421999999999999</v>
+        <v>5.158999999999999</v>
       </c>
       <c r="G8">
         <v>28.5</v>
@@ -1937,28 +1937,28 @@
         <v>3.6675</v>
       </c>
       <c r="M8">
-        <v>0.2224265999999999</v>
+        <v>0.2594976999999999</v>
       </c>
       <c r="N8">
-        <v>3.4450734</v>
+        <v>3.4080023</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>3.4450734</v>
+        <v>3.4080023</v>
       </c>
       <c r="Q8">
-        <v>4.415073399999999</v>
+        <v>4.378002299999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09077419612743297</v>
+        <v>0.09125778963417956</v>
       </c>
       <c r="T8">
-        <v>0.8766307929508996</v>
+        <v>0.8860569305095114</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.48858544796351</v>
+        <v>14.13307324111158</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08839074435978699</v>
+        <v>0.088555744359787</v>
       </c>
       <c r="C9">
-        <v>72.57257081315349</v>
+        <v>71.64557975333673</v>
       </c>
       <c r="D9">
-        <v>49.2315708131535</v>
+        <v>49.04157975333673</v>
       </c>
       <c r="E9">
-        <v>-20.241</v>
+        <v>-19.504</v>
       </c>
       <c r="F9">
-        <v>5.159</v>
+        <v>5.895999999999999</v>
       </c>
       <c r="G9">
         <v>28.5</v>
@@ -2019,45 +2019,45 @@
         <v>3.6675</v>
       </c>
       <c r="M9">
-        <v>0.2594977</v>
+        <v>0.3054127999999999</v>
       </c>
       <c r="N9">
-        <v>3.4080023</v>
+        <v>3.362087199999999</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>3.4080023</v>
+        <v>3.362087199999999</v>
       </c>
       <c r="Q9">
-        <v>4.378002299999999</v>
+        <v>4.332087199999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09125778963417956</v>
+        <v>0.09175189604324674</v>
       </c>
       <c r="T9">
-        <v>0.8860569305095114</v>
+        <v>0.8956879841020061</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0</v>
       </c>
       <c r="W9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>14.13307324111158</v>
+        <v>12.00833756803906</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.088555744359787</v>
+        <v>0.088615744359787</v>
       </c>
       <c r="C10">
-        <v>71.64557975333673</v>
+        <v>70.83985515613077</v>
       </c>
       <c r="D10">
-        <v>49.04157975333673</v>
+        <v>48.97285515613076</v>
       </c>
       <c r="E10">
-        <v>-19.504</v>
+        <v>-18.767</v>
       </c>
       <c r="F10">
-        <v>5.895999999999999</v>
+        <v>6.632999999999999</v>
       </c>
       <c r="G10">
         <v>28.5</v>
@@ -2101,28 +2101,28 @@
         <v>3.6675</v>
       </c>
       <c r="M10">
-        <v>0.3054127999999999</v>
+        <v>0.3435893999999999</v>
       </c>
       <c r="N10">
-        <v>3.362087199999999</v>
+        <v>3.3239106</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>3.362087199999999</v>
+        <v>3.3239106</v>
       </c>
       <c r="Q10">
-        <v>4.332087199999999</v>
+        <v>4.293910599999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09175189604324674</v>
+        <v>0.09225686193383187</v>
       </c>
       <c r="T10">
-        <v>0.8956879841020061</v>
+        <v>0.9055307092020283</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>12.00833756803906</v>
+        <v>10.67407783825694</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.088615744359787</v>
+        <v>0.08884574435978698</v>
       </c>
       <c r="C11">
-        <v>70.83985515613077</v>
+        <v>69.84118569603817</v>
       </c>
       <c r="D11">
-        <v>48.97285515613076</v>
+        <v>48.71118569603817</v>
       </c>
       <c r="E11">
-        <v>-18.767</v>
+        <v>-18.03</v>
       </c>
       <c r="F11">
-        <v>6.632999999999999</v>
+        <v>7.369999999999998</v>
       </c>
       <c r="G11">
         <v>28.5</v>
@@ -2183,45 +2183,45 @@
         <v>3.6675</v>
       </c>
       <c r="M11">
-        <v>0.3435893999999999</v>
+        <v>0.3942949999999999</v>
       </c>
       <c r="N11">
-        <v>3.3239106</v>
+        <v>3.273204999999999</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>3.3239106</v>
+        <v>3.273204999999999</v>
       </c>
       <c r="Q11">
-        <v>4.293910599999999</v>
+        <v>4.243205</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09225686193383187</v>
+        <v>0.09277304928865221</v>
       </c>
       <c r="T11">
-        <v>0.9055307092020283</v>
+        <v>0.9155921615264951</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0</v>
       </c>
       <c r="W11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.67407783825694</v>
+        <v>9.301411379804462</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08884574435978698</v>
+        <v>0.088922744359787</v>
       </c>
       <c r="C12">
-        <v>69.84118569603817</v>
+        <v>69.01720697160212</v>
       </c>
       <c r="D12">
-        <v>48.71118569603817</v>
+        <v>48.62420697160212</v>
       </c>
       <c r="E12">
-        <v>-18.03</v>
+        <v>-17.293</v>
       </c>
       <c r="F12">
-        <v>7.369999999999999</v>
+        <v>8.106999999999999</v>
       </c>
       <c r="G12">
         <v>28.5</v>
@@ -2265,28 +2265,28 @@
         <v>3.6675</v>
       </c>
       <c r="M12">
-        <v>0.394295</v>
+        <v>0.4337245</v>
       </c>
       <c r="N12">
-        <v>3.273204999999999</v>
+        <v>3.2337755</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>3.273204999999999</v>
+        <v>3.2337755</v>
       </c>
       <c r="Q12">
-        <v>4.243205</v>
+        <v>4.203775499999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09277304928865221</v>
+        <v>0.09330083635931123</v>
       </c>
       <c r="T12">
-        <v>0.9155921615264951</v>
+        <v>0.9258797139031975</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.301411379804462</v>
+        <v>8.455828527094965</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.088922744359787</v>
+        <v>0.08899974435978698</v>
       </c>
       <c r="C13">
-        <v>69.01720697160212</v>
+        <v>68.1935383120464</v>
       </c>
       <c r="D13">
-        <v>48.62420697160212</v>
+        <v>48.5375383120464</v>
       </c>
       <c r="E13">
-        <v>-17.293</v>
+        <v>-16.556</v>
       </c>
       <c r="F13">
-        <v>8.106999999999999</v>
+        <v>8.843999999999998</v>
       </c>
       <c r="G13">
         <v>28.5</v>
@@ -2347,28 +2347,28 @@
         <v>3.6675</v>
       </c>
       <c r="M13">
-        <v>0.4337245</v>
+        <v>0.4731539999999999</v>
       </c>
       <c r="N13">
-        <v>3.2337755</v>
+        <v>3.194345999999999</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>3.2337755</v>
+        <v>3.194345999999999</v>
       </c>
       <c r="Q13">
-        <v>4.203775499999999</v>
+        <v>4.164345999999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09330083635931123</v>
+        <v>0.09384061859066703</v>
       </c>
       <c r="T13">
-        <v>0.9258797139031975</v>
+        <v>0.9364010742884609</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.455828527094965</v>
+        <v>7.751176149837052</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08899974435978698</v>
+        <v>0.08918074435978697</v>
       </c>
       <c r="C14">
-        <v>68.1935383120464</v>
+        <v>67.25402232104318</v>
       </c>
       <c r="D14">
-        <v>48.5375383120464</v>
+        <v>48.33502232104318</v>
       </c>
       <c r="E14">
-        <v>-16.556</v>
+        <v>-15.819</v>
       </c>
       <c r="F14">
-        <v>8.843999999999998</v>
+        <v>9.581</v>
       </c>
       <c r="G14">
         <v>28.5</v>
@@ -2429,45 +2429,45 @@
         <v>3.6675</v>
       </c>
       <c r="M14">
-        <v>0.4731539999999999</v>
+        <v>0.5202483</v>
       </c>
       <c r="N14">
-        <v>3.194345999999999</v>
+        <v>3.1472517</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>3.194345999999999</v>
+        <v>3.1472517</v>
       </c>
       <c r="Q14">
-        <v>4.164345999999999</v>
+        <v>4.117251699999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09384061859066703</v>
+        <v>0.09439280960895055</v>
       </c>
       <c r="T14">
-        <v>0.9364010742884609</v>
+        <v>0.9471643050274087</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
       <c r="W14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>7.751176149837052</v>
+        <v>7.049518470315039</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08918074435978697</v>
+        <v>0.089265744359787</v>
       </c>
       <c r="C15">
-        <v>67.25402232104318</v>
+        <v>66.42250014138644</v>
       </c>
       <c r="D15">
-        <v>48.33502232104318</v>
+        <v>48.24050014138643</v>
       </c>
       <c r="E15">
-        <v>-15.819</v>
+        <v>-15.082</v>
       </c>
       <c r="F15">
-        <v>9.581</v>
+        <v>10.318</v>
       </c>
       <c r="G15">
         <v>28.5</v>
@@ -2511,28 +2511,28 @@
         <v>3.6675</v>
       </c>
       <c r="M15">
-        <v>0.5202483</v>
+        <v>0.5602674</v>
       </c>
       <c r="N15">
-        <v>3.1472517</v>
+        <v>3.1072326</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>3.1472517</v>
+        <v>3.1072326</v>
       </c>
       <c r="Q15">
-        <v>4.117251699999999</v>
+        <v>4.077232599999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09439280960895055</v>
+        <v>0.09495784227882209</v>
       </c>
       <c r="T15">
-        <v>0.9471643050274087</v>
+        <v>0.9581778434579601</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.049518470315039</v>
+        <v>6.545981436721108</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.089265744359787</v>
+        <v>0.08950074435978699</v>
       </c>
       <c r="C16">
-        <v>66.42250014138644</v>
+        <v>65.42608768287332</v>
       </c>
       <c r="D16">
-        <v>48.24050014138643</v>
+        <v>47.98108768287333</v>
       </c>
       <c r="E16">
-        <v>-15.082</v>
+        <v>-14.345</v>
       </c>
       <c r="F16">
-        <v>10.318</v>
+        <v>11.055</v>
       </c>
       <c r="G16">
         <v>28.5</v>
@@ -2593,45 +2593,45 @@
         <v>3.6675</v>
       </c>
       <c r="M16">
-        <v>0.5602674</v>
+        <v>0.6113415</v>
       </c>
       <c r="N16">
-        <v>3.1072326</v>
+        <v>3.0561585</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>3.1072326</v>
+        <v>3.0561585</v>
       </c>
       <c r="Q16">
-        <v>4.077232599999999</v>
+        <v>4.026158499999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09495784227882209</v>
+        <v>0.09553616983504351</v>
       </c>
       <c r="T16">
-        <v>0.9581778434579601</v>
+        <v>0.9694505239692301</v>
       </c>
       <c r="U16">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0</v>
       </c>
       <c r="W16">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>6.545981436721108</v>
+        <v>5.999101974919092</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08950074435978699</v>
+        <v>0.08959574435978698</v>
       </c>
       <c r="C17">
-        <v>65.42608768287333</v>
+        <v>64.5850090013369</v>
       </c>
       <c r="D17">
-        <v>47.98108768287333</v>
+        <v>47.8770090013369</v>
       </c>
       <c r="E17">
-        <v>-14.345</v>
+        <v>-13.608</v>
       </c>
       <c r="F17">
-        <v>11.055</v>
+        <v>11.792</v>
       </c>
       <c r="G17">
         <v>28.5</v>
@@ -2675,28 +2675,28 @@
         <v>3.6675</v>
       </c>
       <c r="M17">
-        <v>0.6113414999999999</v>
+        <v>0.6520975999999999</v>
       </c>
       <c r="N17">
-        <v>3.0561585</v>
+        <v>3.0154024</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>3.0561585</v>
+        <v>3.0154024</v>
       </c>
       <c r="Q17">
-        <v>4.026158499999999</v>
+        <v>3.985402399999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09553616983504351</v>
+        <v>0.09612826709498451</v>
       </c>
       <c r="T17">
-        <v>0.9694505239692301</v>
+        <v>0.9809916016355306</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.999101974919093</v>
+        <v>5.624158101486649</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08959574435978698</v>
+        <v>0.08969074435978699</v>
       </c>
       <c r="C18">
-        <v>64.5850090013369</v>
+        <v>63.74438086922223</v>
       </c>
       <c r="D18">
-        <v>47.8770090013369</v>
+        <v>47.77338086922223</v>
       </c>
       <c r="E18">
-        <v>-13.608</v>
+        <v>-12.871</v>
       </c>
       <c r="F18">
-        <v>11.792</v>
+        <v>12.529</v>
       </c>
       <c r="G18">
         <v>28.5</v>
@@ -2757,28 +2757,28 @@
         <v>3.6675</v>
       </c>
       <c r="M18">
-        <v>0.6520975999999999</v>
+        <v>0.6928536999999999</v>
       </c>
       <c r="N18">
-        <v>3.0154024</v>
+        <v>2.9746463</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>3.0154024</v>
+        <v>2.9746463</v>
       </c>
       <c r="Q18">
-        <v>3.985402399999999</v>
+        <v>3.9446463</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09612826709498451</v>
+        <v>0.09673463175877951</v>
       </c>
       <c r="T18">
-        <v>0.9809916016355306</v>
+        <v>0.9928107775588503</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.624158101486649</v>
+        <v>5.293325271987435</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08969074435978699</v>
+        <v>0.08978574435978699</v>
       </c>
       <c r="C19">
-        <v>63.74438086922223</v>
+        <v>62.90420036725202</v>
       </c>
       <c r="D19">
-        <v>47.77338086922223</v>
+        <v>47.67020036725202</v>
       </c>
       <c r="E19">
-        <v>-12.871</v>
+        <v>-12.134</v>
       </c>
       <c r="F19">
-        <v>12.529</v>
+        <v>13.266</v>
       </c>
       <c r="G19">
         <v>28.5</v>
@@ -2839,28 +2839,28 @@
         <v>3.6675</v>
       </c>
       <c r="M19">
-        <v>0.6928536999999999</v>
+        <v>0.7336098</v>
       </c>
       <c r="N19">
-        <v>2.9746463</v>
+        <v>2.9338902</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>2.9746463</v>
+        <v>2.9338902</v>
       </c>
       <c r="Q19">
-        <v>3.9446463</v>
+        <v>3.903890199999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09673463175877951</v>
+        <v>0.09735578580461829</v>
       </c>
       <c r="T19">
-        <v>0.9928107775588503</v>
+        <v>1.004918226065665</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.293325271987435</v>
+        <v>4.999251645765909</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08978574435978701</v>
+        <v>0.08988074435978699</v>
       </c>
       <c r="C20">
-        <v>62.90420036725201</v>
+        <v>62.06446460131473</v>
       </c>
       <c r="D20">
-        <v>47.67020036725201</v>
+        <v>47.56746460131473</v>
       </c>
       <c r="E20">
-        <v>-12.134</v>
+        <v>-11.397</v>
       </c>
       <c r="F20">
-        <v>13.266</v>
+        <v>14.003</v>
       </c>
       <c r="G20">
         <v>28.5</v>
@@ -2921,28 +2921,28 @@
         <v>3.6675</v>
       </c>
       <c r="M20">
-        <v>0.7336098</v>
+        <v>0.7743658999999999</v>
       </c>
       <c r="N20">
-        <v>2.9338902</v>
+        <v>2.8931341</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>2.9338902</v>
+        <v>2.8931341</v>
       </c>
       <c r="Q20">
-        <v>3.903890199999999</v>
+        <v>3.863134099999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09735578580461829</v>
+        <v>0.09799227698739134</v>
       </c>
       <c r="T20">
-        <v>1.004918226065665</v>
+        <v>1.017324623918328</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.999251645765909</v>
+        <v>4.73613313809402</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08988074435978699</v>
+        <v>0.09047574435978699</v>
       </c>
       <c r="C21">
-        <v>62.06446460131473</v>
+        <v>60.69395212506247</v>
       </c>
       <c r="D21">
-        <v>47.56746460131473</v>
+        <v>46.93395212506245</v>
       </c>
       <c r="E21">
-        <v>-11.397</v>
+        <v>-10.66</v>
       </c>
       <c r="F21">
-        <v>14.003</v>
+        <v>14.74</v>
       </c>
       <c r="G21">
         <v>28.5</v>
@@ -3003,45 +3003,45 @@
         <v>3.6675</v>
       </c>
       <c r="M21">
-        <v>0.7743658999999999</v>
+        <v>0.851972</v>
       </c>
       <c r="N21">
-        <v>2.8931341</v>
+        <v>2.815528</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>2.8931341</v>
+        <v>2.815528</v>
       </c>
       <c r="Q21">
-        <v>3.863134099999999</v>
+        <v>3.785527999999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09799227698739134</v>
+        <v>0.09864468044973373</v>
       </c>
       <c r="T21">
-        <v>1.017324623918328</v>
+        <v>1.030041181717307</v>
       </c>
       <c r="U21">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
       <c r="W21">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.73613313809402</v>
+        <v>4.304718934425075</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09047574435978699</v>
+        <v>0.090595744359787</v>
       </c>
       <c r="C22">
-        <v>60.69395212506247</v>
+        <v>59.83122423873082</v>
       </c>
       <c r="D22">
-        <v>46.93395212506245</v>
+        <v>46.80822423873082</v>
       </c>
       <c r="E22">
-        <v>-10.66</v>
+        <v>-9.923</v>
       </c>
       <c r="F22">
-        <v>14.74</v>
+        <v>15.477</v>
       </c>
       <c r="G22">
         <v>28.5</v>
@@ -3085,28 +3085,28 @@
         <v>3.6675</v>
       </c>
       <c r="M22">
-        <v>0.851972</v>
+        <v>0.8945706</v>
       </c>
       <c r="N22">
-        <v>2.815528</v>
+        <v>2.7729294</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>2.815528</v>
+        <v>2.7729294</v>
       </c>
       <c r="Q22">
-        <v>3.785527999999999</v>
+        <v>3.7429294</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09864468044973373</v>
+        <v>0.09931360045542659</v>
       </c>
       <c r="T22">
-        <v>1.030041181717307</v>
+        <v>1.043079677688412</v>
       </c>
       <c r="U22">
         <v>0.0578</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.304718934425075</v>
+        <v>4.099732318500071</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.090595744359787</v>
+        <v>0.09148574435978699</v>
       </c>
       <c r="C23">
-        <v>59.83122423873082</v>
+        <v>58.18235730614039</v>
       </c>
       <c r="D23">
-        <v>46.80822423873082</v>
+        <v>45.89635730614039</v>
       </c>
       <c r="E23">
-        <v>-9.923000000000002</v>
+        <v>-9.186</v>
       </c>
       <c r="F23">
-        <v>15.477</v>
+        <v>16.214</v>
       </c>
       <c r="G23">
         <v>28.5</v>
@@ -3167,45 +3167,45 @@
         <v>3.6675</v>
       </c>
       <c r="M23">
-        <v>0.8945705999999999</v>
+        <v>0.9939182</v>
       </c>
       <c r="N23">
-        <v>2.7729294</v>
+        <v>2.6735818</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>2.7729294</v>
+        <v>2.6735818</v>
       </c>
       <c r="Q23">
-        <v>3.7429294</v>
+        <v>3.643581799999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09931360045542659</v>
+        <v>0.09999967225613716</v>
       </c>
       <c r="T23">
-        <v>1.043079677688412</v>
+        <v>1.056452494069033</v>
       </c>
       <c r="U23">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V23">
         <v>0</v>
       </c>
       <c r="W23">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.099732318500072</v>
+        <v>3.689941486130347</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09148574435978699</v>
+        <v>0.09164074435978699</v>
       </c>
       <c r="C24">
-        <v>58.18235730614039</v>
+        <v>57.29016926367282</v>
       </c>
       <c r="D24">
-        <v>45.89635730614039</v>
+        <v>45.74116926367281</v>
       </c>
       <c r="E24">
-        <v>-9.186</v>
+        <v>-8.449000000000002</v>
       </c>
       <c r="F24">
-        <v>16.214</v>
+        <v>16.951</v>
       </c>
       <c r="G24">
         <v>28.5</v>
@@ -3249,28 +3249,28 @@
         <v>3.6675</v>
       </c>
       <c r="M24">
-        <v>0.9939182</v>
+        <v>1.0390963</v>
       </c>
       <c r="N24">
-        <v>2.6735818</v>
+        <v>2.6284037</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>2.6735818</v>
+        <v>2.6284037</v>
       </c>
       <c r="Q24">
-        <v>3.643581799999999</v>
+        <v>3.5984037</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09999967225613716</v>
+        <v>0.1007035641036195</v>
       </c>
       <c r="T24">
-        <v>1.056452494069033</v>
+        <v>1.07017265632967</v>
       </c>
       <c r="U24">
         <v>0.0613</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.689941486130347</v>
+        <v>3.529509247602942</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09164074435978699</v>
+        <v>0.092467744359787</v>
       </c>
       <c r="C25">
-        <v>57.29016926367282</v>
+        <v>55.74258911886398</v>
       </c>
       <c r="D25">
-        <v>45.74116926367281</v>
+        <v>44.93058911886398</v>
       </c>
       <c r="E25">
-        <v>-8.449000000000002</v>
+        <v>-7.712</v>
       </c>
       <c r="F25">
-        <v>16.951</v>
+        <v>17.688</v>
       </c>
       <c r="G25">
         <v>28.5</v>
@@ -3331,45 +3331,45 @@
         <v>3.6675</v>
       </c>
       <c r="M25">
-        <v>1.0390963</v>
+        <v>1.1338008</v>
       </c>
       <c r="N25">
-        <v>2.6284037</v>
+        <v>2.5336992</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>2.6284037</v>
+        <v>2.5336992</v>
       </c>
       <c r="Q25">
-        <v>3.5984037</v>
+        <v>3.503699199999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1007035641036195</v>
+        <v>0.1014259794207724</v>
       </c>
       <c r="T25">
-        <v>1.07017265632967</v>
+        <v>1.084253875491902</v>
       </c>
       <c r="U25">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V25">
         <v>0</v>
       </c>
       <c r="W25">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.529509247602942</v>
+        <v>3.234695195134806</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.092467744359787</v>
+        <v>0.09265074435978699</v>
       </c>
       <c r="C26">
-        <v>55.74258911886398</v>
+        <v>54.83008928591343</v>
       </c>
       <c r="D26">
-        <v>44.93058911886398</v>
+        <v>44.75508928591343</v>
       </c>
       <c r="E26">
-        <v>-7.712000000000003</v>
+        <v>-6.975000000000001</v>
       </c>
       <c r="F26">
-        <v>17.688</v>
+        <v>18.425</v>
       </c>
       <c r="G26">
         <v>28.5</v>
@@ -3413,28 +3413,28 @@
         <v>3.6675</v>
       </c>
       <c r="M26">
-        <v>1.1338008</v>
+        <v>1.1810425</v>
       </c>
       <c r="N26">
-        <v>2.5336992</v>
+        <v>2.486457499999999</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>2.5336992</v>
+        <v>2.486457499999999</v>
       </c>
       <c r="Q26">
-        <v>3.5036992</v>
+        <v>3.456457499999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1014259794207724</v>
+        <v>0.1021676591463827</v>
       </c>
       <c r="T26">
-        <v>1.084253875491902</v>
+        <v>1.098710593831794</v>
       </c>
       <c r="U26">
         <v>0.0641</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.234695195134807</v>
+        <v>3.105307387329414</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09265074435978699</v>
+        <v>0.09486174435978699</v>
       </c>
       <c r="C27">
-        <v>54.83008928591343</v>
+        <v>52.07617154883719</v>
       </c>
       <c r="D27">
-        <v>44.75508928591343</v>
+        <v>42.73817154883718</v>
       </c>
       <c r="E27">
-        <v>-6.975000000000001</v>
+        <v>-6.238</v>
       </c>
       <c r="F27">
-        <v>18.425</v>
+        <v>19.162</v>
       </c>
       <c r="G27">
         <v>28.5</v>
@@ -3495,45 +3495,45 @@
         <v>3.6675</v>
       </c>
       <c r="M27">
-        <v>1.1810425</v>
+        <v>1.3777478</v>
       </c>
       <c r="N27">
-        <v>2.486457499999999</v>
+        <v>2.2897522</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>2.486457499999999</v>
+        <v>2.2897522</v>
       </c>
       <c r="Q27">
-        <v>3.456457499999999</v>
+        <v>3.259752199999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1021676591463827</v>
+        <v>0.1029293842699824</v>
       </c>
       <c r="T27">
-        <v>1.098710593831794</v>
+        <v>1.113558034288981</v>
       </c>
       <c r="U27">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V27">
         <v>0</v>
       </c>
       <c r="W27">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.105307387329414</v>
+        <v>2.661953080237181</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09486174435978699</v>
+        <v>0.095122744359787</v>
       </c>
       <c r="C28">
-        <v>52.07617154883719</v>
+        <v>51.11301497707632</v>
       </c>
       <c r="D28">
-        <v>42.73817154883718</v>
+        <v>42.51201497707632</v>
       </c>
       <c r="E28">
-        <v>-6.238</v>
+        <v>-5.501000000000001</v>
       </c>
       <c r="F28">
-        <v>19.162</v>
+        <v>19.899</v>
       </c>
       <c r="G28">
         <v>28.5</v>
@@ -3577,28 +3577,28 @@
         <v>3.6675</v>
       </c>
       <c r="M28">
-        <v>1.3777478</v>
+        <v>1.4307381</v>
       </c>
       <c r="N28">
-        <v>2.2897522</v>
+        <v>2.236761899999999</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>2.2897522</v>
+        <v>2.236761899999999</v>
       </c>
       <c r="Q28">
-        <v>3.259752199999999</v>
+        <v>3.206761899999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1029293842699824</v>
+        <v>0.1037119785750507</v>
       </c>
       <c r="T28">
-        <v>1.113558034288981</v>
+        <v>1.128812253936775</v>
       </c>
       <c r="U28">
         <v>0.07190000000000001</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.661953080237181</v>
+        <v>2.563362225413582</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.095122744359787</v>
+        <v>0.09647574435978699</v>
       </c>
       <c r="C29">
-        <v>51.11301497707632</v>
+        <v>49.24097972518908</v>
       </c>
       <c r="D29">
-        <v>42.51201497707632</v>
+        <v>41.37697972518908</v>
       </c>
       <c r="E29">
-        <v>-5.501000000000001</v>
+        <v>-4.763999999999999</v>
       </c>
       <c r="F29">
-        <v>19.899</v>
+        <v>20.636</v>
       </c>
       <c r="G29">
         <v>28.5</v>
@@ -3659,45 +3659,45 @@
         <v>3.6675</v>
       </c>
       <c r="M29">
-        <v>1.4307381</v>
+        <v>1.5642088</v>
       </c>
       <c r="N29">
-        <v>2.236761899999999</v>
+        <v>2.103291199999999</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>2.236761899999999</v>
+        <v>2.103291199999999</v>
       </c>
       <c r="Q29">
-        <v>3.206761899999999</v>
+        <v>3.073291199999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1037119785750507</v>
+        <v>0.1045163116108153</v>
       </c>
       <c r="T29">
-        <v>1.128812253936775</v>
+        <v>1.144490201908119</v>
       </c>
       <c r="U29">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V29">
         <v>0</v>
       </c>
       <c r="W29">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.563362225413582</v>
+        <v>2.344635831226623</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09647574435978699</v>
+        <v>0.09677574435978699</v>
       </c>
       <c r="C30">
-        <v>49.24097972518908</v>
+        <v>48.2604699133471</v>
       </c>
       <c r="D30">
-        <v>41.37697972518908</v>
+        <v>41.1334699133471</v>
       </c>
       <c r="E30">
-        <v>-4.763999999999999</v>
+        <v>-4.027000000000001</v>
       </c>
       <c r="F30">
-        <v>20.636</v>
+        <v>21.373</v>
       </c>
       <c r="G30">
         <v>28.5</v>
@@ -3741,28 +3741,28 @@
         <v>3.6675</v>
       </c>
       <c r="M30">
-        <v>1.5642088</v>
+        <v>1.6200734</v>
       </c>
       <c r="N30">
-        <v>2.103291199999999</v>
+        <v>2.0474266</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>2.103291199999999</v>
+        <v>2.0474266</v>
       </c>
       <c r="Q30">
-        <v>3.073291199999999</v>
+        <v>3.017426599999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1045163116108153</v>
+        <v>0.1053433019151929</v>
       </c>
       <c r="T30">
-        <v>1.144490201908119</v>
+        <v>1.160609782216684</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.344635831226623</v>
+        <v>2.263786319805016</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09677574435978699</v>
+        <v>0.09707574435978698</v>
       </c>
       <c r="C31">
-        <v>48.26046991334711</v>
+        <v>47.28280951673896</v>
       </c>
       <c r="D31">
-        <v>41.1334699133471</v>
+        <v>40.89280951673896</v>
       </c>
       <c r="E31">
-        <v>-4.027000000000005</v>
+        <v>-3.290000000000003</v>
       </c>
       <c r="F31">
-        <v>21.37299999999999</v>
+        <v>22.11</v>
       </c>
       <c r="G31">
         <v>28.5</v>
@@ -3823,28 +3823,28 @@
         <v>3.6675</v>
       </c>
       <c r="M31">
-        <v>1.6200734</v>
+        <v>1.675938</v>
       </c>
       <c r="N31">
-        <v>2.0474266</v>
+        <v>1.991562</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>2.0474266</v>
+        <v>1.991562</v>
       </c>
       <c r="Q31">
-        <v>3.017426599999999</v>
+        <v>2.961561999999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1053433019151929</v>
+        <v>0.1061939205139814</v>
       </c>
       <c r="T31">
-        <v>1.160609782216684</v>
+        <v>1.177189921962637</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.263786319805016</v>
+        <v>2.188326775811515</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09707574435978698</v>
+        <v>0.09737574435978699</v>
       </c>
       <c r="C32">
-        <v>47.28280951673896</v>
+        <v>46.30794881288867</v>
       </c>
       <c r="D32">
-        <v>40.89280951673896</v>
+        <v>40.65494881288866</v>
       </c>
       <c r="E32">
-        <v>-3.290000000000003</v>
+        <v>-2.553000000000001</v>
       </c>
       <c r="F32">
-        <v>22.11</v>
+        <v>22.847</v>
       </c>
       <c r="G32">
         <v>28.5</v>
@@ -3905,28 +3905,28 @@
         <v>3.6675</v>
       </c>
       <c r="M32">
-        <v>1.675938</v>
+        <v>1.7318026</v>
       </c>
       <c r="N32">
-        <v>1.991562</v>
+        <v>1.9356974</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>1.991562</v>
+        <v>1.9356974</v>
       </c>
       <c r="Q32">
-        <v>2.961561999999999</v>
+        <v>2.905697399999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1061939205139814</v>
+        <v>0.107069194724329</v>
       </c>
       <c r="T32">
-        <v>1.177189921962637</v>
+        <v>1.194250645469342</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.188326775811515</v>
+        <v>2.117735589495015</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09737574435978699</v>
+        <v>0.09767574435978699</v>
       </c>
       <c r="C33">
-        <v>46.30794881288867</v>
+        <v>45.33583922951042</v>
       </c>
       <c r="D33">
-        <v>40.65494881288866</v>
+        <v>40.41983922951041</v>
       </c>
       <c r="E33">
-        <v>-2.553000000000001</v>
+        <v>-1.816000000000003</v>
       </c>
       <c r="F33">
-        <v>22.847</v>
+        <v>23.584</v>
       </c>
       <c r="G33">
         <v>28.5</v>
@@ -3987,28 +3987,28 @@
         <v>3.6675</v>
       </c>
       <c r="M33">
-        <v>1.7318026</v>
+        <v>1.7876672</v>
       </c>
       <c r="N33">
-        <v>1.9356974</v>
+        <v>1.8798328</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>1.9356974</v>
+        <v>1.8798328</v>
       </c>
       <c r="Q33">
-        <v>2.905697399999999</v>
+        <v>2.8498328</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.107069194724329</v>
+        <v>0.1079702122938044</v>
       </c>
       <c r="T33">
-        <v>1.194250645469342</v>
+        <v>1.211813154961538</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.117735589495015</v>
+        <v>2.051556352323296</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09767574435978699</v>
+        <v>0.102661744359787</v>
       </c>
       <c r="C34">
-        <v>45.33583922951042</v>
+        <v>41.05457021934504</v>
       </c>
       <c r="D34">
-        <v>40.41983922951041</v>
+        <v>36.87557021934503</v>
       </c>
       <c r="E34">
-        <v>-1.816000000000003</v>
+        <v>-1.079000000000001</v>
       </c>
       <c r="F34">
-        <v>23.584</v>
+        <v>24.321</v>
       </c>
       <c r="G34">
         <v>28.5</v>
@@ -4069,45 +4069,45 @@
         <v>3.6675</v>
       </c>
       <c r="M34">
-        <v>1.7876672</v>
+        <v>2.18889</v>
       </c>
       <c r="N34">
-        <v>1.8798328</v>
+        <v>1.47861</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>1.8798328</v>
+        <v>1.47861</v>
       </c>
       <c r="Q34">
-        <v>2.8498328</v>
+        <v>2.44861</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1079702122938044</v>
+        <v>0.1088981259101298</v>
       </c>
       <c r="T34">
-        <v>1.211813154961538</v>
+        <v>1.229899918468427</v>
       </c>
       <c r="U34">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V34">
         <v>0</v>
       </c>
       <c r="W34">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.051556352323296</v>
+        <v>1.67550676370215</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.102661744359787</v>
+        <v>0.103103744359787</v>
       </c>
       <c r="C35">
-        <v>41.05457021934504</v>
+        <v>40.03313850865933</v>
       </c>
       <c r="D35">
-        <v>36.87557021934503</v>
+        <v>36.59113850865933</v>
       </c>
       <c r="E35">
-        <v>-1.079000000000001</v>
+        <v>-0.3420000000000023</v>
       </c>
       <c r="F35">
-        <v>24.321</v>
+        <v>25.058</v>
       </c>
       <c r="G35">
         <v>28.5</v>
@@ -4151,28 +4151,28 @@
         <v>3.6675</v>
       </c>
       <c r="M35">
-        <v>2.18889</v>
+        <v>2.25522</v>
       </c>
       <c r="N35">
-        <v>1.47861</v>
+        <v>1.41228</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>1.47861</v>
+        <v>1.41228</v>
       </c>
       <c r="Q35">
-        <v>2.44861</v>
+        <v>2.38228</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1088981259101298</v>
+        <v>0.1098541581208894</v>
       </c>
       <c r="T35">
-        <v>1.229899918468427</v>
+        <v>1.248534765717948</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.67550676370215</v>
+        <v>1.626227153005028</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.103103744359787</v>
+        <v>0.103545744359787</v>
       </c>
       <c r="C36">
-        <v>40.03313850865933</v>
+        <v>39.01606101723314</v>
       </c>
       <c r="D36">
-        <v>36.59113850865933</v>
+        <v>36.31106101723314</v>
       </c>
       <c r="E36">
-        <v>-0.3420000000000023</v>
+        <v>0.3949999999999996</v>
       </c>
       <c r="F36">
-        <v>25.058</v>
+        <v>25.795</v>
       </c>
       <c r="G36">
         <v>28.5</v>
@@ -4233,28 +4233,28 @@
         <v>3.6675</v>
       </c>
       <c r="M36">
-        <v>2.25522</v>
+        <v>2.32155</v>
       </c>
       <c r="N36">
-        <v>1.41228</v>
+        <v>1.34595</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>1.41228</v>
+        <v>1.34595</v>
       </c>
       <c r="Q36">
-        <v>2.38228</v>
+        <v>2.31595</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1098541581208894</v>
+        <v>0.1108396067073646</v>
       </c>
       <c r="T36">
-        <v>1.248534765717948</v>
+        <v>1.267742992882839</v>
       </c>
       <c r="U36">
         <v>0.09</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.626227153005028</v>
+        <v>1.579763520062027</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.103545744359787</v>
+        <v>0.103987744359787</v>
       </c>
       <c r="C37">
-        <v>39.01606101723314</v>
+        <v>38.00323851979485</v>
       </c>
       <c r="D37">
-        <v>36.31106101723314</v>
+        <v>36.03523851979485</v>
       </c>
       <c r="E37">
-        <v>0.3949999999999996</v>
+        <v>1.132000000000001</v>
       </c>
       <c r="F37">
-        <v>25.795</v>
+        <v>26.532</v>
       </c>
       <c r="G37">
         <v>28.5</v>
@@ -4315,28 +4315,28 @@
         <v>3.6675</v>
       </c>
       <c r="M37">
-        <v>2.32155</v>
+        <v>2.38788</v>
       </c>
       <c r="N37">
-        <v>1.34595</v>
+        <v>1.27962</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>1.34595</v>
+        <v>1.27962</v>
       </c>
       <c r="Q37">
-        <v>2.31595</v>
+        <v>2.249619999999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1108396067073646</v>
+        <v>0.1118558505621672</v>
       </c>
       <c r="T37">
-        <v>1.267742992882839</v>
+        <v>1.287551477146634</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.579763520062027</v>
+        <v>1.535881200060304</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.103987744359787</v>
+        <v>0.125445744359787</v>
       </c>
       <c r="C38">
-        <v>38.00323851979485</v>
+        <v>27.55769534057927</v>
       </c>
       <c r="D38">
-        <v>36.03523851979485</v>
+        <v>26.32669534057926</v>
       </c>
       <c r="E38">
-        <v>1.131999999999998</v>
+        <v>1.868999999999996</v>
       </c>
       <c r="F38">
-        <v>26.532</v>
+        <v>27.26899999999999</v>
       </c>
       <c r="G38">
         <v>28.5</v>
@@ -4397,45 +4397,45 @@
         <v>3.6675</v>
       </c>
       <c r="M38">
-        <v>2.38788</v>
+        <v>4.0030892</v>
       </c>
       <c r="N38">
-        <v>1.27962</v>
+        <v>-0.3355892000000003</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P38">
-        <v>1.27962</v>
+        <v>-0.3355892000000003</v>
       </c>
       <c r="Q38">
-        <v>2.24962</v>
+        <v>0.6344107999999995</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1118558505621672</v>
+        <v>0.112904356126646</v>
       </c>
       <c r="T38">
-        <v>1.287551477146634</v>
+        <v>1.307988802180708</v>
       </c>
       <c r="U38">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V38">
         <v>0</v>
       </c>
       <c r="W38">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y38">
-        <v>1.535881200060305</v>
+        <v>0.916167443883089</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.125445744359787</v>
+        <v>0.126455744359787</v>
       </c>
       <c r="C39">
-        <v>27.55769534057927</v>
+        <v>26.49102307104601</v>
       </c>
       <c r="D39">
-        <v>26.32669534057926</v>
+        <v>25.99702307104601</v>
       </c>
       <c r="E39">
-        <v>1.868999999999996</v>
+        <v>2.605999999999998</v>
       </c>
       <c r="F39">
-        <v>27.26899999999999</v>
+        <v>28.006</v>
       </c>
       <c r="G39">
         <v>28.5</v>
@@ -4479,28 +4479,28 @@
         <v>3.6675</v>
       </c>
       <c r="M39">
-        <v>4.0030892</v>
+        <v>4.1112808</v>
       </c>
       <c r="N39">
-        <v>-0.3355892000000003</v>
+        <v>-0.4437808000000008</v>
       </c>
       <c r="O39">
         <v>-0</v>
       </c>
       <c r="P39">
-        <v>-0.3355892000000003</v>
+        <v>-0.4437808000000008</v>
       </c>
       <c r="Q39">
-        <v>0.6344107999999995</v>
+        <v>0.526219199999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.112904356126646</v>
+        <v>0.1139866844512693</v>
       </c>
       <c r="T39">
-        <v>1.307988802180708</v>
+        <v>1.329085395764267</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.916167443883089</v>
+        <v>0.8920577743072181</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.126455744359787</v>
+        <v>0.127465744359787</v>
       </c>
       <c r="C40">
-        <v>26.49102307104601</v>
+        <v>25.43250523627212</v>
       </c>
       <c r="D40">
-        <v>25.99702307104601</v>
+        <v>25.67550523627212</v>
       </c>
       <c r="E40">
-        <v>2.605999999999998</v>
+        <v>3.342999999999996</v>
       </c>
       <c r="F40">
-        <v>28.006</v>
+        <v>28.74299999999999</v>
       </c>
       <c r="G40">
         <v>28.5</v>
@@ -4561,28 +4561,28 @@
         <v>3.6675</v>
       </c>
       <c r="M40">
-        <v>4.1112808</v>
+        <v>4.2194724</v>
       </c>
       <c r="N40">
-        <v>-0.4437808000000008</v>
+        <v>-0.5519724000000004</v>
       </c>
       <c r="O40">
         <v>-0</v>
       </c>
       <c r="P40">
-        <v>-0.4437808000000008</v>
+        <v>-0.5519724000000004</v>
       </c>
       <c r="Q40">
-        <v>0.526219199999999</v>
+        <v>0.4180275999999994</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1139866844512693</v>
+        <v>0.1151044989504705</v>
       </c>
       <c r="T40">
-        <v>1.329085395764267</v>
+        <v>1.350873680940731</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8920577743072181</v>
+        <v>0.8691844980429306</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.127465744359787</v>
+        <v>0.128475744359787</v>
       </c>
       <c r="C41">
-        <v>25.43250523627212</v>
+        <v>24.38184298273639</v>
       </c>
       <c r="D41">
-        <v>25.67550523627212</v>
+        <v>25.36184298273639</v>
       </c>
       <c r="E41">
-        <v>3.342999999999996</v>
+        <v>4.079999999999998</v>
       </c>
       <c r="F41">
-        <v>28.74299999999999</v>
+        <v>29.48</v>
       </c>
       <c r="G41">
         <v>28.5</v>
@@ -4643,28 +4643,28 @@
         <v>3.6675</v>
       </c>
       <c r="M41">
-        <v>4.2194724</v>
+        <v>4.327664</v>
       </c>
       <c r="N41">
-        <v>-0.5519724000000004</v>
+        <v>-0.660164</v>
       </c>
       <c r="O41">
         <v>-0</v>
       </c>
       <c r="P41">
-        <v>-0.5519724000000004</v>
+        <v>-0.660164</v>
       </c>
       <c r="Q41">
-        <v>0.4180275999999994</v>
+        <v>0.3098359999999998</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1151044989504705</v>
+        <v>0.1162595739329783</v>
       </c>
       <c r="T41">
-        <v>1.350873680940731</v>
+        <v>1.373388242289743</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8691844980429306</v>
+        <v>0.8474548855918573</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.128475744359787</v>
+        <v>0.129485744359787</v>
       </c>
       <c r="C42">
-        <v>24.38184298273639</v>
+        <v>23.33875188432378</v>
       </c>
       <c r="D42">
-        <v>25.36184298273639</v>
+        <v>25.05575188432378</v>
       </c>
       <c r="E42">
-        <v>4.079999999999998</v>
+        <v>4.817</v>
       </c>
       <c r="F42">
-        <v>29.48</v>
+        <v>30.217</v>
       </c>
       <c r="G42">
         <v>28.5</v>
@@ -4725,28 +4725,28 @@
         <v>3.6675</v>
       </c>
       <c r="M42">
-        <v>4.327664</v>
+        <v>4.4358556</v>
       </c>
       <c r="N42">
-        <v>-0.660164</v>
+        <v>-0.7683556000000005</v>
       </c>
       <c r="O42">
         <v>-0</v>
       </c>
       <c r="P42">
-        <v>-0.660164</v>
+        <v>-0.7683556000000005</v>
       </c>
       <c r="Q42">
-        <v>0.3098359999999998</v>
+        <v>0.2016443999999993</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1162595739329783</v>
+        <v>0.117453803999639</v>
       </c>
       <c r="T42">
-        <v>1.373388242289743</v>
+        <v>1.396666009108213</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8474548855918573</v>
+        <v>0.8267852542359584</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.129485744359787</v>
+        <v>0.130495744359787</v>
       </c>
       <c r="C43">
-        <v>23.33875188432378</v>
+        <v>22.3029610820886</v>
       </c>
       <c r="D43">
-        <v>25.05575188432378</v>
+        <v>24.75696108208859</v>
       </c>
       <c r="E43">
-        <v>4.817</v>
+        <v>5.553999999999998</v>
       </c>
       <c r="F43">
-        <v>30.217</v>
+        <v>30.954</v>
       </c>
       <c r="G43">
         <v>28.5</v>
@@ -4807,28 +4807,28 @@
         <v>3.6675</v>
       </c>
       <c r="M43">
-        <v>4.4358556</v>
+        <v>4.5440472</v>
       </c>
       <c r="N43">
-        <v>-0.7683556000000005</v>
+        <v>-0.8765472000000001</v>
       </c>
       <c r="O43">
         <v>-0</v>
       </c>
       <c r="P43">
-        <v>-0.7683556000000005</v>
+        <v>-0.8765472000000001</v>
       </c>
       <c r="Q43">
-        <v>0.2016443999999993</v>
+        <v>0.09345279999999967</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.117453803999639</v>
+        <v>0.1186892144134259</v>
       </c>
       <c r="T43">
-        <v>1.396666009108213</v>
+        <v>1.420746457541113</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8267852542359584</v>
+        <v>0.8070998910398641</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.130495744359787</v>
+        <v>0.154725744359787</v>
       </c>
       <c r="C44">
-        <v>22.3029610820886</v>
+        <v>16.05889596589682</v>
       </c>
       <c r="D44">
-        <v>24.75696108208859</v>
+        <v>19.24989596589681</v>
       </c>
       <c r="E44">
-        <v>5.553999999999995</v>
+        <v>6.290999999999997</v>
       </c>
       <c r="F44">
-        <v>30.95399999999999</v>
+        <v>31.691</v>
       </c>
       <c r="G44">
         <v>28.5</v>
@@ -4889,45 +4889,45 @@
         <v>3.6675</v>
       </c>
       <c r="M44">
-        <v>4.5440472</v>
+        <v>6.363552799999999</v>
       </c>
       <c r="N44">
-        <v>-0.8765472000000001</v>
+        <v>-2.696052799999999</v>
       </c>
       <c r="O44">
         <v>-0</v>
       </c>
       <c r="P44">
-        <v>-0.8765472000000001</v>
+        <v>-2.696052799999999</v>
       </c>
       <c r="Q44">
-        <v>0.09345279999999967</v>
+        <v>-1.7260528</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1186892144134258</v>
+        <v>0.1199679725610298</v>
       </c>
       <c r="T44">
-        <v>1.420746457541113</v>
+        <v>1.445671833989203</v>
       </c>
       <c r="U44">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V44">
         <v>0</v>
       </c>
       <c r="W44">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.8070998910398641</v>
+        <v>0.576328996594481</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.154725744359787</v>
+        <v>0.156275744359787</v>
       </c>
       <c r="C45">
-        <v>16.05889596589682</v>
+        <v>15.05181551592973</v>
       </c>
       <c r="D45">
-        <v>19.24989596589681</v>
+        <v>18.97981551592973</v>
       </c>
       <c r="E45">
-        <v>6.290999999999997</v>
+        <v>7.027999999999999</v>
       </c>
       <c r="F45">
-        <v>31.691</v>
+        <v>32.428</v>
       </c>
       <c r="G45">
         <v>28.5</v>
@@ -4971,28 +4971,28 @@
         <v>3.6675</v>
       </c>
       <c r="M45">
-        <v>6.363552799999999</v>
+        <v>6.5115424</v>
       </c>
       <c r="N45">
-        <v>-2.696052799999999</v>
+        <v>-2.8440424</v>
       </c>
       <c r="O45">
         <v>-0</v>
       </c>
       <c r="P45">
-        <v>-2.696052799999999</v>
+        <v>-2.8440424</v>
       </c>
       <c r="Q45">
-        <v>-1.7260528</v>
+        <v>-1.8740424</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1199679725610298</v>
+        <v>0.1212924006424768</v>
       </c>
       <c r="T45">
-        <v>1.445671833989203</v>
+        <v>1.471487402453296</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.576328996594481</v>
+        <v>0.5632306103082427</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.156275744359787</v>
+        <v>0.157825744359787</v>
       </c>
       <c r="C46">
-        <v>15.05181551592973</v>
+        <v>14.05220878907586</v>
       </c>
       <c r="D46">
-        <v>18.97981551592973</v>
+        <v>18.71720878907586</v>
       </c>
       <c r="E46">
-        <v>7.027999999999999</v>
+        <v>7.765000000000001</v>
       </c>
       <c r="F46">
-        <v>32.428</v>
+        <v>33.165</v>
       </c>
       <c r="G46">
         <v>28.5</v>
@@ -5053,28 +5053,28 @@
         <v>3.6675</v>
       </c>
       <c r="M46">
-        <v>6.5115424</v>
+        <v>6.659532</v>
       </c>
       <c r="N46">
-        <v>-2.8440424</v>
+        <v>-2.992032000000001</v>
       </c>
       <c r="O46">
         <v>-0</v>
       </c>
       <c r="P46">
-        <v>-2.8440424</v>
+        <v>-2.992032000000001</v>
       </c>
       <c r="Q46">
-        <v>-1.8740424</v>
+        <v>-2.022032000000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1212924006424768</v>
+        <v>0.1226649897450673</v>
       </c>
       <c r="T46">
-        <v>1.471487402453296</v>
+        <v>1.498241718861538</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5632306103082427</v>
+        <v>0.550714374523615</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.157825744359787</v>
+        <v>0.159375744359787</v>
       </c>
       <c r="C47">
-        <v>14.05220878907586</v>
+        <v>13.05976979735626</v>
       </c>
       <c r="D47">
-        <v>18.71720878907586</v>
+        <v>18.46176979735626</v>
       </c>
       <c r="E47">
-        <v>7.765000000000001</v>
+        <v>8.501999999999995</v>
       </c>
       <c r="F47">
-        <v>33.165</v>
+        <v>33.90199999999999</v>
       </c>
       <c r="G47">
         <v>28.5</v>
@@ -5135,28 +5135,28 @@
         <v>3.6675</v>
       </c>
       <c r="M47">
-        <v>6.659532</v>
+        <v>6.807521599999999</v>
       </c>
       <c r="N47">
-        <v>-2.992032000000001</v>
+        <v>-3.1400216</v>
       </c>
       <c r="O47">
         <v>-0</v>
       </c>
       <c r="P47">
-        <v>-2.992032000000001</v>
+        <v>-3.1400216</v>
       </c>
       <c r="Q47">
-        <v>-2.022032000000001</v>
+        <v>-2.1700216</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1226649897450673</v>
+        <v>0.124088415481087</v>
       </c>
       <c r="T47">
-        <v>1.498241718861538</v>
+        <v>1.525986935877492</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.550714374523615</v>
+        <v>0.5387423229035366</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.159375744359787</v>
+        <v>0.160925744359787</v>
       </c>
       <c r="C48">
-        <v>13.05976979735626</v>
+        <v>12.07420903151684</v>
       </c>
       <c r="D48">
-        <v>18.46176979735626</v>
+        <v>18.21320903151683</v>
       </c>
       <c r="E48">
-        <v>8.501999999999995</v>
+        <v>9.238999999999997</v>
       </c>
       <c r="F48">
-        <v>33.90199999999999</v>
+        <v>34.639</v>
       </c>
       <c r="G48">
         <v>28.5</v>
@@ -5217,28 +5217,28 @@
         <v>3.6675</v>
       </c>
       <c r="M48">
-        <v>6.807521599999999</v>
+        <v>6.955511199999999</v>
       </c>
       <c r="N48">
-        <v>-3.1400216</v>
+        <v>-3.2880112</v>
       </c>
       <c r="O48">
         <v>-0</v>
       </c>
       <c r="P48">
-        <v>-3.1400216</v>
+        <v>-3.2880112</v>
       </c>
       <c r="Q48">
-        <v>-2.1700216</v>
+        <v>-2.3180112</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.124088415481087</v>
+        <v>0.1255655553958245</v>
       </c>
       <c r="T48">
-        <v>1.525986935877492</v>
+        <v>1.554779142214803</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5387423229035366</v>
+        <v>0.5272797202885677</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.160925744359787</v>
+        <v>0.162475744359787</v>
       </c>
       <c r="C49">
-        <v>12.07420903151684</v>
+        <v>11.09525236645543</v>
       </c>
       <c r="D49">
-        <v>18.21320903151683</v>
+        <v>17.97125236645543</v>
       </c>
       <c r="E49">
-        <v>9.238999999999997</v>
+        <v>9.975999999999999</v>
       </c>
       <c r="F49">
-        <v>34.639</v>
+        <v>35.376</v>
       </c>
       <c r="G49">
         <v>28.5</v>
@@ -5299,28 +5299,28 @@
         <v>3.6675</v>
       </c>
       <c r="M49">
-        <v>6.955511199999999</v>
+        <v>7.1035008</v>
       </c>
       <c r="N49">
-        <v>-3.2880112</v>
+        <v>-3.4360008</v>
       </c>
       <c r="O49">
         <v>-0</v>
       </c>
       <c r="P49">
-        <v>-3.2880112</v>
+        <v>-3.4360008</v>
       </c>
       <c r="Q49">
-        <v>-2.3180112</v>
+        <v>-2.466000800000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1255655553958245</v>
+        <v>0.1270995083842058</v>
       </c>
       <c r="T49">
-        <v>1.554779142214803</v>
+        <v>1.584678741103549</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5272797202885677</v>
+        <v>0.5162947261158892</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.162475744359787</v>
+        <v>0.164025744359787</v>
       </c>
       <c r="C50">
-        <v>11.09525236645544</v>
+        <v>10.12264005275128</v>
       </c>
       <c r="D50">
-        <v>17.97125236645543</v>
+        <v>17.73564005275127</v>
       </c>
       <c r="E50">
-        <v>9.975999999999992</v>
+        <v>10.71299999999999</v>
       </c>
       <c r="F50">
-        <v>35.37599999999999</v>
+        <v>36.11299999999999</v>
       </c>
       <c r="G50">
         <v>28.5</v>
@@ -5381,28 +5381,28 @@
         <v>3.6675</v>
       </c>
       <c r="M50">
-        <v>7.103500799999998</v>
+        <v>7.251490399999999</v>
       </c>
       <c r="N50">
-        <v>-3.436000799999999</v>
+        <v>-3.583990399999999</v>
       </c>
       <c r="O50">
         <v>-0</v>
       </c>
       <c r="P50">
-        <v>-3.436000799999999</v>
+        <v>-3.583990399999999</v>
       </c>
       <c r="Q50">
-        <v>-2.466000799999999</v>
+        <v>-2.6139904</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1270995083842058</v>
+        <v>0.1286936163917392</v>
       </c>
       <c r="T50">
-        <v>1.584678741103549</v>
+        <v>1.61575087328205</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5162947261158892</v>
+        <v>0.5057580990522996</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.164025744359787</v>
+        <v>0.183075744359787</v>
       </c>
       <c r="C51">
-        <v>10.12264005275128</v>
+        <v>6.924433635109125</v>
       </c>
       <c r="D51">
-        <v>17.73564005275127</v>
+        <v>15.27443363510912</v>
       </c>
       <c r="E51">
-        <v>10.71299999999999</v>
+        <v>11.45</v>
       </c>
       <c r="F51">
-        <v>36.11299999999999</v>
+        <v>36.84999999999999</v>
       </c>
       <c r="G51">
         <v>28.5</v>
@@ -5463,45 +5463,45 @@
         <v>3.6675</v>
       </c>
       <c r="M51">
-        <v>7.251490399999999</v>
+        <v>8.689229999999998</v>
       </c>
       <c r="N51">
-        <v>-3.583990399999999</v>
+        <v>-5.021729999999999</v>
       </c>
       <c r="O51">
         <v>-0</v>
       </c>
       <c r="P51">
-        <v>-3.583990399999999</v>
+        <v>-5.021729999999999</v>
       </c>
       <c r="Q51">
-        <v>-2.6139904</v>
+        <v>-4.051729999999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1286936163917392</v>
+        <v>0.130351488719574</v>
       </c>
       <c r="T51">
-        <v>1.61575087328205</v>
+        <v>1.648065890747691</v>
       </c>
       <c r="U51">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V51">
         <v>0</v>
       </c>
       <c r="W51">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.5057580990522996</v>
+        <v>0.4220742229173357</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.183075744359787</v>
+        <v>0.184975744359787</v>
       </c>
       <c r="C52">
-        <v>6.924433635109125</v>
+        <v>5.97891005910666</v>
       </c>
       <c r="D52">
-        <v>15.27443363510912</v>
+        <v>15.06591005910666</v>
       </c>
       <c r="E52">
-        <v>11.45</v>
+        <v>12.187</v>
       </c>
       <c r="F52">
-        <v>36.84999999999999</v>
+        <v>37.587</v>
       </c>
       <c r="G52">
         <v>28.5</v>
@@ -5545,28 +5545,28 @@
         <v>3.6675</v>
       </c>
       <c r="M52">
-        <v>8.689229999999998</v>
+        <v>8.8630146</v>
       </c>
       <c r="N52">
-        <v>-5.021729999999999</v>
+        <v>-5.1955146</v>
       </c>
       <c r="O52">
         <v>-0</v>
       </c>
       <c r="P52">
-        <v>-5.021729999999999</v>
+        <v>-5.1955146</v>
       </c>
       <c r="Q52">
-        <v>-4.051729999999999</v>
+        <v>-4.2255146</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.130351488719574</v>
+        <v>0.1320770293056877</v>
       </c>
       <c r="T52">
-        <v>1.648065890747691</v>
+        <v>1.681699888518052</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4220742229173357</v>
+        <v>0.4137982577620937</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.184975744359787</v>
+        <v>0.186875744359787</v>
       </c>
       <c r="C53">
-        <v>5.97891005910666</v>
+        <v>5.039003250128218</v>
       </c>
       <c r="D53">
-        <v>15.06591005910666</v>
+        <v>14.86300325012821</v>
       </c>
       <c r="E53">
-        <v>12.187</v>
+        <v>12.924</v>
       </c>
       <c r="F53">
-        <v>37.587</v>
+        <v>38.324</v>
       </c>
       <c r="G53">
         <v>28.5</v>
@@ -5627,28 +5627,28 @@
         <v>3.6675</v>
       </c>
       <c r="M53">
-        <v>8.8630146</v>
+        <v>9.036799199999999</v>
       </c>
       <c r="N53">
-        <v>-5.1955146</v>
+        <v>-5.369299199999999</v>
       </c>
       <c r="O53">
         <v>-0</v>
       </c>
       <c r="P53">
-        <v>-5.1955146</v>
+        <v>-5.369299199999999</v>
       </c>
       <c r="Q53">
-        <v>-4.2255146</v>
+        <v>-4.3992992</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1320770293056877</v>
+        <v>0.1338744674162229</v>
       </c>
       <c r="T53">
-        <v>1.681699888518052</v>
+        <v>1.716735302862179</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4137982577620937</v>
+        <v>0.4058405989589765</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.186875744359787</v>
+        <v>0.188775744359787</v>
       </c>
       <c r="C54">
-        <v>5.039003250128218</v>
+        <v>4.104489285072859</v>
       </c>
       <c r="D54">
-        <v>14.86300325012821</v>
+        <v>14.66548928507285</v>
       </c>
       <c r="E54">
-        <v>12.924</v>
+        <v>13.66099999999999</v>
       </c>
       <c r="F54">
-        <v>38.324</v>
+        <v>39.06099999999999</v>
       </c>
       <c r="G54">
         <v>28.5</v>
@@ -5709,28 +5709,28 @@
         <v>3.6675</v>
       </c>
       <c r="M54">
-        <v>9.036799199999999</v>
+        <v>9.210583799999998</v>
       </c>
       <c r="N54">
-        <v>-5.369299199999999</v>
+        <v>-5.543083799999999</v>
       </c>
       <c r="O54">
         <v>-0</v>
       </c>
       <c r="P54">
-        <v>-5.369299199999999</v>
+        <v>-5.543083799999999</v>
       </c>
       <c r="Q54">
-        <v>-4.3992992</v>
+        <v>-4.573083799999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1338744674162229</v>
+        <v>0.1357483922548659</v>
       </c>
       <c r="T54">
-        <v>1.716735302862179</v>
+        <v>1.753261585901799</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4058405989589765</v>
+        <v>0.3981832291672978</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.188775744359787</v>
+        <v>0.190675744359787</v>
       </c>
       <c r="C55">
-        <v>4.104489285072859</v>
+        <v>3.175155987564892</v>
       </c>
       <c r="D55">
-        <v>14.66548928507285</v>
+        <v>14.47315598756489</v>
       </c>
       <c r="E55">
-        <v>13.66099999999999</v>
+        <v>14.398</v>
       </c>
       <c r="F55">
-        <v>39.06099999999999</v>
+        <v>39.79799999999999</v>
       </c>
       <c r="G55">
         <v>28.5</v>
@@ -5791,28 +5791,28 @@
         <v>3.6675</v>
       </c>
       <c r="M55">
-        <v>9.210583799999998</v>
+        <v>9.3843684</v>
       </c>
       <c r="N55">
-        <v>-5.543083799999999</v>
+        <v>-5.7168684</v>
       </c>
       <c r="O55">
         <v>-0</v>
       </c>
       <c r="P55">
-        <v>-5.543083799999999</v>
+        <v>-5.7168684</v>
       </c>
       <c r="Q55">
-        <v>-4.573083799999999</v>
+        <v>-4.7468684</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1357483922548659</v>
+        <v>0.1377037920864935</v>
       </c>
       <c r="T55">
-        <v>1.753261585901799</v>
+        <v>1.791375968204012</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3981832291672978</v>
+        <v>0.3908094656641996</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.190675744359787</v>
+        <v>0.192575744359787</v>
       </c>
       <c r="C56">
-        <v>3.175155987564892</v>
+        <v>2.250802167651933</v>
       </c>
       <c r="D56">
-        <v>14.47315598756489</v>
+        <v>14.28580216765193</v>
       </c>
       <c r="E56">
-        <v>14.398</v>
+        <v>15.135</v>
       </c>
       <c r="F56">
-        <v>39.79799999999999</v>
+        <v>40.535</v>
       </c>
       <c r="G56">
         <v>28.5</v>
@@ -5873,28 +5873,28 @@
         <v>3.6675</v>
       </c>
       <c r="M56">
-        <v>9.3843684</v>
+        <v>9.558152999999999</v>
       </c>
       <c r="N56">
-        <v>-5.7168684</v>
+        <v>-5.890652999999999</v>
       </c>
       <c r="O56">
         <v>-0</v>
       </c>
       <c r="P56">
-        <v>-5.7168684</v>
+        <v>-5.890652999999999</v>
       </c>
       <c r="Q56">
-        <v>-4.7468684</v>
+        <v>-4.920653</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1377037920864935</v>
+        <v>0.1397460985773044</v>
       </c>
       <c r="T56">
-        <v>1.791375968204012</v>
+        <v>1.83118432305299</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3908094656641996</v>
+        <v>0.3837038390157597</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.192575744359787</v>
+        <v>0.194475744359787</v>
       </c>
       <c r="C57">
-        <v>2.250802167651933</v>
+        <v>1.331236919800517</v>
       </c>
       <c r="D57">
-        <v>14.28580216765193</v>
+        <v>14.10323691980052</v>
       </c>
       <c r="E57">
-        <v>15.135</v>
+        <v>15.872</v>
       </c>
       <c r="F57">
-        <v>40.535</v>
+        <v>41.272</v>
       </c>
       <c r="G57">
         <v>28.5</v>
@@ -5955,28 +5955,28 @@
         <v>3.6675</v>
       </c>
       <c r="M57">
-        <v>9.558152999999999</v>
+        <v>9.7319376</v>
       </c>
       <c r="N57">
-        <v>-5.890652999999999</v>
+        <v>-6.064437600000001</v>
       </c>
       <c r="O57">
         <v>-0</v>
       </c>
       <c r="P57">
-        <v>-5.890652999999999</v>
+        <v>-6.064437600000001</v>
       </c>
       <c r="Q57">
-        <v>-4.920653</v>
+        <v>-5.094437600000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1397460985773044</v>
+        <v>0.1418812371813341</v>
       </c>
       <c r="T57">
-        <v>1.83118432305299</v>
+        <v>1.872802148576922</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3837038390157597</v>
+        <v>0.376851984747621</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.194475744359787</v>
+        <v>0.196375744359787</v>
       </c>
       <c r="C58">
-        <v>1.331236919800517</v>
+        <v>0.4162789740400399</v>
       </c>
       <c r="D58">
-        <v>14.10323691980052</v>
+        <v>13.92527897404004</v>
       </c>
       <c r="E58">
-        <v>15.872</v>
+        <v>16.609</v>
       </c>
       <c r="F58">
-        <v>41.272</v>
+        <v>42.009</v>
       </c>
       <c r="G58">
         <v>28.5</v>
@@ -6037,28 +6037,28 @@
         <v>3.6675</v>
       </c>
       <c r="M58">
-        <v>9.7319376</v>
+        <v>9.905722200000001</v>
       </c>
       <c r="N58">
-        <v>-6.064437600000001</v>
+        <v>-6.238222200000002</v>
       </c>
       <c r="O58">
         <v>-0</v>
       </c>
       <c r="P58">
-        <v>-6.064437600000001</v>
+        <v>-6.238222200000002</v>
       </c>
       <c r="Q58">
-        <v>-5.094437600000001</v>
+        <v>-5.268222200000002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1418812371813341</v>
+        <v>0.1441156845576442</v>
       </c>
       <c r="T58">
-        <v>1.872802148576922</v>
+        <v>1.916355686915921</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.376851984747621</v>
+        <v>0.3702405464187153</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.196375744359787</v>
+        <v>0.198275744359787</v>
       </c>
       <c r="C59">
-        <v>0.4162789740400399</v>
+        <v>-0.4942439043808236</v>
       </c>
       <c r="D59">
-        <v>13.92527897404004</v>
+        <v>13.75175609561917</v>
       </c>
       <c r="E59">
-        <v>16.609</v>
+        <v>17.346</v>
       </c>
       <c r="F59">
-        <v>42.009</v>
+        <v>42.746</v>
       </c>
       <c r="G59">
         <v>28.5</v>
@@ -6119,28 +6119,28 @@
         <v>3.6675</v>
       </c>
       <c r="M59">
-        <v>9.905722200000001</v>
+        <v>10.0795068</v>
       </c>
       <c r="N59">
-        <v>-6.238222200000002</v>
+        <v>-6.412006799999999</v>
       </c>
       <c r="O59">
         <v>-0</v>
       </c>
       <c r="P59">
-        <v>-6.238222200000002</v>
+        <v>-6.412006799999999</v>
       </c>
       <c r="Q59">
-        <v>-5.268222200000002</v>
+        <v>-5.4420068</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1441156845576442</v>
+        <v>0.146456534189969</v>
       </c>
       <c r="T59">
-        <v>1.916355686915921</v>
+        <v>1.961983203271061</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3702405464187153</v>
+        <v>0.363857088721841</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.198275744359787</v>
+        <v>0.200175744359787</v>
       </c>
       <c r="C60">
-        <v>-0.4942439043808164</v>
+        <v>-1.400495471005051</v>
       </c>
       <c r="D60">
-        <v>13.75175609561917</v>
+        <v>13.58250452899494</v>
       </c>
       <c r="E60">
-        <v>17.34599999999999</v>
+        <v>18.08299999999999</v>
       </c>
       <c r="F60">
-        <v>42.74599999999999</v>
+        <v>43.48299999999999</v>
       </c>
       <c r="G60">
         <v>28.5</v>
@@ -6201,28 +6201,28 @@
         <v>3.6675</v>
       </c>
       <c r="M60">
-        <v>10.0795068</v>
+        <v>10.2532914</v>
       </c>
       <c r="N60">
-        <v>-6.412006799999998</v>
+        <v>-6.585791399999999</v>
       </c>
       <c r="O60">
         <v>-0</v>
       </c>
       <c r="P60">
-        <v>-6.412006799999998</v>
+        <v>-6.585791399999999</v>
       </c>
       <c r="Q60">
-        <v>-5.442006799999998</v>
+        <v>-5.615791399999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.146456534189969</v>
+        <v>0.1489115716092365</v>
       </c>
       <c r="T60">
-        <v>1.961983203271061</v>
+        <v>2.009836452131331</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3638570887218411</v>
+        <v>0.3576900194214708</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.200175744359787</v>
+        <v>0.202075744359787</v>
       </c>
       <c r="C61">
-        <v>-1.400495471005051</v>
+        <v>-2.302631517618124</v>
       </c>
       <c r="D61">
-        <v>13.58250452899494</v>
+        <v>13.41736848238187</v>
       </c>
       <c r="E61">
-        <v>18.08299999999999</v>
+        <v>18.81999999999999</v>
       </c>
       <c r="F61">
-        <v>43.48299999999999</v>
+        <v>44.21999999999999</v>
       </c>
       <c r="G61">
         <v>28.5</v>
@@ -6283,28 +6283,28 @@
         <v>3.6675</v>
       </c>
       <c r="M61">
-        <v>10.2532914</v>
+        <v>10.427076</v>
       </c>
       <c r="N61">
-        <v>-6.585791399999999</v>
+        <v>-6.759575999999998</v>
       </c>
       <c r="O61">
         <v>-0</v>
       </c>
       <c r="P61">
-        <v>-6.585791399999999</v>
+        <v>-6.759575999999998</v>
       </c>
       <c r="Q61">
-        <v>-5.615791399999999</v>
+        <v>-5.789575999999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1489115716092365</v>
+        <v>0.1514893608994675</v>
       </c>
       <c r="T61">
-        <v>2.009836452131331</v>
+        <v>2.060082363434614</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3576900194214708</v>
+        <v>0.3517285190977797</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.202075744359787</v>
+        <v>0.203975744359787</v>
       </c>
       <c r="C62">
-        <v>-2.302631517618124</v>
+        <v>-3.200800350549549</v>
       </c>
       <c r="D62">
-        <v>13.41736848238187</v>
+        <v>13.25619964945044</v>
       </c>
       <c r="E62">
-        <v>18.81999999999999</v>
+        <v>19.557</v>
       </c>
       <c r="F62">
-        <v>44.21999999999999</v>
+        <v>44.95699999999999</v>
       </c>
       <c r="G62">
         <v>28.5</v>
@@ -6365,28 +6365,28 @@
         <v>3.6675</v>
       </c>
       <c r="M62">
-        <v>10.427076</v>
+        <v>10.6008606</v>
       </c>
       <c r="N62">
-        <v>-6.759575999999998</v>
+        <v>-6.933360599999999</v>
       </c>
       <c r="O62">
         <v>-0</v>
       </c>
       <c r="P62">
-        <v>-6.759575999999998</v>
+        <v>-6.933360599999999</v>
       </c>
       <c r="Q62">
-        <v>-5.789575999999999</v>
+        <v>-5.9633606</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1514893608994675</v>
+        <v>0.1541993445122743</v>
       </c>
       <c r="T62">
-        <v>2.060082363434614</v>
+        <v>2.112904988138065</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3517285190977797</v>
+        <v>0.3459624778010948</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.203975744359787</v>
+        <v>0.205875744359787</v>
       </c>
       <c r="C63">
-        <v>-3.200800350549549</v>
+        <v>-4.095143234911504</v>
       </c>
       <c r="D63">
-        <v>13.25619964945044</v>
+        <v>13.09885676508849</v>
       </c>
       <c r="E63">
-        <v>19.557</v>
+        <v>20.294</v>
       </c>
       <c r="F63">
-        <v>44.95699999999999</v>
+        <v>45.694</v>
       </c>
       <c r="G63">
         <v>28.5</v>
@@ -6447,28 +6447,28 @@
         <v>3.6675</v>
       </c>
       <c r="M63">
-        <v>10.6008606</v>
+        <v>10.7746452</v>
       </c>
       <c r="N63">
-        <v>-6.933360599999999</v>
+        <v>-7.107145200000001</v>
       </c>
       <c r="O63">
         <v>-0</v>
       </c>
       <c r="P63">
-        <v>-6.933360599999999</v>
+        <v>-7.107145200000001</v>
       </c>
       <c r="Q63">
-        <v>-5.9633606</v>
+        <v>-6.137145200000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1541993445122743</v>
+        <v>0.1570519588415447</v>
       </c>
       <c r="T63">
-        <v>2.112904988138065</v>
+        <v>2.168507750983804</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3459624778010948</v>
+        <v>0.340382437836561</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.205875744359787</v>
+        <v>0.207775744359787</v>
       </c>
       <c r="C64">
-        <v>-4.095143234911504</v>
+        <v>-4.985794807571587</v>
       </c>
       <c r="D64">
-        <v>13.09885676508849</v>
+        <v>12.94520519242841</v>
       </c>
       <c r="E64">
-        <v>20.294</v>
+        <v>21.03099999999999</v>
       </c>
       <c r="F64">
-        <v>45.694</v>
+        <v>46.43099999999999</v>
       </c>
       <c r="G64">
         <v>28.5</v>
@@ -6529,28 +6529,28 @@
         <v>3.6675</v>
       </c>
       <c r="M64">
-        <v>10.7746452</v>
+        <v>10.9484298</v>
       </c>
       <c r="N64">
-        <v>-7.107145200000001</v>
+        <v>-7.280929799999998</v>
       </c>
       <c r="O64">
         <v>-0</v>
       </c>
       <c r="P64">
-        <v>-7.107145200000001</v>
+        <v>-7.280929799999998</v>
       </c>
       <c r="Q64">
-        <v>-6.137145200000001</v>
+        <v>-6.310929799999998</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1570519588415447</v>
+        <v>0.1600587685399648</v>
       </c>
       <c r="T64">
-        <v>2.168507750983804</v>
+        <v>2.227116068577961</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.340382437836561</v>
+        <v>0.3349795419978854</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.207775744359787</v>
+        <v>0.209675744359787</v>
       </c>
       <c r="C65">
-        <v>-4.985794807571587</v>
+        <v>-5.872883461397095</v>
       </c>
       <c r="D65">
-        <v>12.94520519242841</v>
+        <v>12.7951165386029</v>
       </c>
       <c r="E65">
-        <v>21.03099999999999</v>
+        <v>21.76799999999999</v>
       </c>
       <c r="F65">
-        <v>46.43099999999999</v>
+        <v>47.16799999999999</v>
       </c>
       <c r="G65">
         <v>28.5</v>
@@ -6611,28 +6611,28 @@
         <v>3.6675</v>
       </c>
       <c r="M65">
-        <v>10.9484298</v>
+        <v>11.1222144</v>
       </c>
       <c r="N65">
-        <v>-7.280929799999998</v>
+        <v>-7.454714399999999</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>-7.280929799999998</v>
+        <v>-7.454714399999999</v>
       </c>
       <c r="Q65">
-        <v>-6.310929799999998</v>
+        <v>-6.4847144</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1600587685399648</v>
+        <v>0.1632326232216305</v>
       </c>
       <c r="T65">
-        <v>2.227116068577961</v>
+        <v>2.288980403816238</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3349795419978854</v>
+        <v>0.3297454866541685</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.209675744359787</v>
+        <v>0.211575744359787</v>
       </c>
       <c r="C66">
-        <v>-5.872883461397095</v>
+        <v>-6.756531703075829</v>
       </c>
       <c r="D66">
-        <v>12.7951165386029</v>
+        <v>12.64846829692416</v>
       </c>
       <c r="E66">
-        <v>21.76799999999999</v>
+        <v>22.505</v>
       </c>
       <c r="F66">
-        <v>47.16799999999999</v>
+        <v>47.90499999999999</v>
       </c>
       <c r="G66">
         <v>28.5</v>
@@ -6693,28 +6693,28 @@
         <v>3.6675</v>
       </c>
       <c r="M66">
-        <v>11.1222144</v>
+        <v>11.295999</v>
       </c>
       <c r="N66">
-        <v>-7.454714399999999</v>
+        <v>-7.628498999999999</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>-7.454714399999999</v>
+        <v>-7.628498999999999</v>
       </c>
       <c r="Q66">
-        <v>-6.4847144</v>
+        <v>-6.658498999999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1632326232216305</v>
+        <v>0.1665878410279629</v>
       </c>
       <c r="T66">
-        <v>2.288980403816238</v>
+        <v>2.354379843925274</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3297454866541685</v>
+        <v>0.3246724791671812</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.211575744359787</v>
+        <v>0.213475744359787</v>
       </c>
       <c r="C67">
-        <v>-6.756531703075829</v>
+        <v>-7.636856486609155</v>
       </c>
       <c r="D67">
-        <v>12.64846829692416</v>
+        <v>12.50514351339084</v>
       </c>
       <c r="E67">
-        <v>22.505</v>
+        <v>23.242</v>
       </c>
       <c r="F67">
-        <v>47.90499999999999</v>
+        <v>48.642</v>
       </c>
       <c r="G67">
         <v>28.5</v>
@@ -6775,28 +6775,28 @@
         <v>3.6675</v>
       </c>
       <c r="M67">
-        <v>11.295999</v>
+        <v>11.4697836</v>
       </c>
       <c r="N67">
-        <v>-7.628498999999999</v>
+        <v>-7.8022836</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-7.628498999999999</v>
+        <v>-7.8022836</v>
       </c>
       <c r="Q67">
-        <v>-6.658498999999999</v>
+        <v>-6.8322836</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1665878410279629</v>
+        <v>0.1701404245876088</v>
       </c>
       <c r="T67">
-        <v>2.354379843925274</v>
+        <v>2.423626309923076</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3246724791671812</v>
+        <v>0.3197531991797997</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.213475744359787</v>
+        <v>0.215375744359787</v>
       </c>
       <c r="C68">
-        <v>-7.636856486609155</v>
+        <v>-8.513969524385551</v>
       </c>
       <c r="D68">
-        <v>12.50514351339084</v>
+        <v>12.36503047561445</v>
       </c>
       <c r="E68">
-        <v>23.242</v>
+        <v>23.979</v>
       </c>
       <c r="F68">
-        <v>48.642</v>
+        <v>49.379</v>
       </c>
       <c r="G68">
         <v>28.5</v>
@@ -6857,28 +6857,28 @@
         <v>3.6675</v>
       </c>
       <c r="M68">
-        <v>11.4697836</v>
+        <v>11.6435682</v>
       </c>
       <c r="N68">
-        <v>-7.8022836</v>
+        <v>-7.976068200000001</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-7.8022836</v>
+        <v>-7.976068200000001</v>
       </c>
       <c r="Q68">
-        <v>-6.8322836</v>
+        <v>-7.006068200000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1701404245876088</v>
+        <v>0.1739083162417788</v>
       </c>
       <c r="T68">
-        <v>2.423626309923076</v>
+        <v>2.497069531435896</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3197531991797997</v>
+        <v>0.3149807633711459</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.215375744359787</v>
+        <v>0.217275744359787</v>
       </c>
       <c r="C69">
-        <v>-8.513969524385551</v>
+        <v>-9.387977577573373</v>
       </c>
       <c r="D69">
-        <v>12.36503047561445</v>
+        <v>12.22802242242662</v>
       </c>
       <c r="E69">
-        <v>23.979</v>
+        <v>24.71599999999999</v>
       </c>
       <c r="F69">
-        <v>49.379</v>
+        <v>50.11599999999999</v>
       </c>
       <c r="G69">
         <v>28.5</v>
@@ -6939,28 +6939,28 @@
         <v>3.6675</v>
       </c>
       <c r="M69">
-        <v>11.6435682</v>
+        <v>11.8173528</v>
       </c>
       <c r="N69">
-        <v>-7.976068200000001</v>
+        <v>-8.149852799999998</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-7.976068200000001</v>
+        <v>-8.149852799999998</v>
       </c>
       <c r="Q69">
-        <v>-7.006068200000001</v>
+        <v>-7.179852799999998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1739083162417788</v>
+        <v>0.1779117011243344</v>
       </c>
       <c r="T69">
-        <v>2.497069531435896</v>
+        <v>2.575102954293268</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3149807633711459</v>
+        <v>0.3103486933215703</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.217275744359787</v>
+        <v>0.219175744359787</v>
       </c>
       <c r="C70">
-        <v>-9.387977577573373</v>
+        <v>-10.25898272741946</v>
       </c>
       <c r="D70">
-        <v>12.22802242242662</v>
+        <v>12.09401727258053</v>
       </c>
       <c r="E70">
-        <v>24.71599999999999</v>
+        <v>25.453</v>
       </c>
       <c r="F70">
-        <v>50.11599999999999</v>
+        <v>50.85299999999999</v>
       </c>
       <c r="G70">
         <v>28.5</v>
@@ -7021,28 +7021,28 @@
         <v>3.6675</v>
       </c>
       <c r="M70">
-        <v>11.8173528</v>
+        <v>11.9911374</v>
       </c>
       <c r="N70">
-        <v>-8.149852799999998</v>
+        <v>-8.323637399999999</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-8.149852799999998</v>
+        <v>-8.323637399999999</v>
       </c>
       <c r="Q70">
-        <v>-7.179852799999998</v>
+        <v>-7.353637399999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1779117011243344</v>
+        <v>0.1821733689025387</v>
       </c>
       <c r="T70">
-        <v>2.575102954293268</v>
+        <v>2.658170791528535</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3103486933215703</v>
+        <v>0.3058508861719824</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.219175744359787</v>
+        <v>0.221075744359787</v>
       </c>
       <c r="C71">
-        <v>-10.25898272741946</v>
+        <v>-11.12708262890231</v>
       </c>
       <c r="D71">
-        <v>12.09401727258053</v>
+        <v>11.96291737109768</v>
       </c>
       <c r="E71">
-        <v>25.453</v>
+        <v>26.19</v>
       </c>
       <c r="F71">
-        <v>50.85299999999999</v>
+        <v>51.59</v>
       </c>
       <c r="G71">
         <v>28.5</v>
@@ -7103,28 +7103,28 @@
         <v>3.6675</v>
       </c>
       <c r="M71">
-        <v>11.9911374</v>
+        <v>12.164922</v>
       </c>
       <c r="N71">
-        <v>-8.323637399999999</v>
+        <v>-8.497422</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-8.323637399999999</v>
+        <v>-8.497422</v>
       </c>
       <c r="Q71">
-        <v>-7.353637399999999</v>
+        <v>-7.527422000000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1821733689025387</v>
+        <v>0.1867191478659567</v>
       </c>
       <c r="T71">
-        <v>2.658170791528535</v>
+        <v>2.746776484579486</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3058508861719824</v>
+        <v>0.3014815877980968</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.221075744359787</v>
+        <v>0.222975744359787</v>
       </c>
       <c r="C72">
-        <v>-11.12708262890231</v>
+        <v>-11.99237074806455</v>
       </c>
       <c r="D72">
-        <v>11.96291737109768</v>
+        <v>11.83462925193545</v>
       </c>
       <c r="E72">
-        <v>26.19</v>
+        <v>26.927</v>
       </c>
       <c r="F72">
-        <v>51.59</v>
+        <v>52.327</v>
       </c>
       <c r="G72">
         <v>28.5</v>
@@ -7185,28 +7185,28 @@
         <v>3.6675</v>
       </c>
       <c r="M72">
-        <v>12.164922</v>
+        <v>12.3387066</v>
       </c>
       <c r="N72">
-        <v>-8.497422</v>
+        <v>-8.671206600000001</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-8.497422</v>
+        <v>-8.671206600000001</v>
       </c>
       <c r="Q72">
-        <v>-7.527422000000001</v>
+        <v>-7.701206600000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1867191478659567</v>
+        <v>0.1915784288268517</v>
       </c>
       <c r="T72">
-        <v>2.746776484579486</v>
+        <v>2.841492915082227</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3014815877980968</v>
+        <v>0.2972353682516446</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.222975744359787</v>
+        <v>0.224875744359787</v>
       </c>
       <c r="C73">
-        <v>-11.99237074806454</v>
+        <v>-12.85493658423665</v>
       </c>
       <c r="D73">
-        <v>11.83462925193545</v>
+        <v>11.70906341576334</v>
       </c>
       <c r="E73">
-        <v>26.92699999999999</v>
+        <v>27.66399999999999</v>
       </c>
       <c r="F73">
-        <v>52.32699999999999</v>
+        <v>53.06399999999999</v>
       </c>
       <c r="G73">
         <v>28.5</v>
@@ -7267,28 +7267,28 @@
         <v>3.6675</v>
       </c>
       <c r="M73">
-        <v>12.3387066</v>
+        <v>12.5124912</v>
       </c>
       <c r="N73">
-        <v>-8.671206599999998</v>
+        <v>-8.844991199999999</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-8.671206599999998</v>
+        <v>-8.844991199999999</v>
       </c>
       <c r="Q73">
-        <v>-7.701206599999998</v>
+        <v>-7.874991199999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1915784288268517</v>
+        <v>0.1967848012849535</v>
       </c>
       <c r="T73">
-        <v>2.841492915082226</v>
+        <v>2.942974804906591</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2972353682516449</v>
+        <v>0.2931070992481498</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.224875744359787</v>
+        <v>0.226775744359787</v>
       </c>
       <c r="C74">
-        <v>-12.85493658423665</v>
+        <v>-13.71486587826249</v>
       </c>
       <c r="D74">
-        <v>11.70906341576334</v>
+        <v>11.5861341217375</v>
       </c>
       <c r="E74">
-        <v>27.66399999999999</v>
+        <v>28.40099999999999</v>
       </c>
       <c r="F74">
-        <v>53.06399999999999</v>
+        <v>53.80099999999999</v>
       </c>
       <c r="G74">
         <v>28.5</v>
@@ -7349,28 +7349,28 @@
         <v>3.6675</v>
       </c>
       <c r="M74">
-        <v>12.5124912</v>
+        <v>12.6862758</v>
       </c>
       <c r="N74">
-        <v>-8.844991199999999</v>
+        <v>-9.018775799999997</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-8.844991199999999</v>
+        <v>-9.018775799999997</v>
       </c>
       <c r="Q74">
-        <v>-7.874991199999999</v>
+        <v>-8.048775799999998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1967848012849535</v>
+        <v>0.202376830962174</v>
       </c>
       <c r="T74">
-        <v>2.942974804906591</v>
+        <v>3.051973871754984</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2931070992481498</v>
+        <v>0.2890919335050245</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.226775744359787</v>
+        <v>0.228675744359787</v>
       </c>
       <c r="C75">
-        <v>-13.71486587826249</v>
+        <v>-14.57224080774461</v>
       </c>
       <c r="D75">
-        <v>11.5861341217375</v>
+        <v>11.46575919225538</v>
       </c>
       <c r="E75">
-        <v>28.40099999999999</v>
+        <v>29.13799999999999</v>
       </c>
       <c r="F75">
-        <v>53.80099999999999</v>
+        <v>54.53799999999999</v>
       </c>
       <c r="G75">
         <v>28.5</v>
@@ -7431,28 +7431,28 @@
         <v>3.6675</v>
       </c>
       <c r="M75">
-        <v>12.6862758</v>
+        <v>12.8600604</v>
       </c>
       <c r="N75">
-        <v>-9.018775799999997</v>
+        <v>-9.192560399999998</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-9.018775799999997</v>
+        <v>-9.192560399999998</v>
       </c>
       <c r="Q75">
-        <v>-8.048775799999998</v>
+        <v>-8.222560399999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.202376830962174</v>
+        <v>0.2083990167684115</v>
       </c>
       <c r="T75">
-        <v>3.051973871754984</v>
+        <v>3.169357482207098</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2890919335050245</v>
+        <v>0.2851852857549566</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.228675744359787</v>
+        <v>0.230575744359787</v>
       </c>
       <c r="C76">
-        <v>-14.57224080774461</v>
+        <v>-15.42714017024355</v>
       </c>
       <c r="D76">
-        <v>11.46575919225538</v>
+        <v>11.34785982975644</v>
       </c>
       <c r="E76">
-        <v>29.13799999999999</v>
+        <v>29.87499999999999</v>
       </c>
       <c r="F76">
-        <v>54.53799999999999</v>
+        <v>55.27499999999999</v>
       </c>
       <c r="G76">
         <v>28.5</v>
@@ -7513,28 +7513,28 @@
         <v>3.6675</v>
       </c>
       <c r="M76">
-        <v>12.8600604</v>
+        <v>13.033845</v>
       </c>
       <c r="N76">
-        <v>-9.192560399999998</v>
+        <v>-9.366344999999999</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-9.192560399999998</v>
+        <v>-9.366344999999999</v>
       </c>
       <c r="Q76">
-        <v>-8.222560399999999</v>
+        <v>-8.396345</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2083990167684115</v>
+        <v>0.214902977439148</v>
       </c>
       <c r="T76">
-        <v>3.169357482207098</v>
+        <v>3.296131781495383</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2851852857549566</v>
+        <v>0.2813828152782237</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.230575744359787</v>
+        <v>0.232475744359787</v>
       </c>
       <c r="C77">
-        <v>-15.42714017024355</v>
+        <v>-16.27963955528944</v>
       </c>
       <c r="D77">
-        <v>11.34785982975644</v>
+        <v>11.23236044471056</v>
       </c>
       <c r="E77">
-        <v>29.87499999999999</v>
+        <v>30.61199999999999</v>
       </c>
       <c r="F77">
-        <v>55.27499999999999</v>
+        <v>56.01199999999999</v>
       </c>
       <c r="G77">
         <v>28.5</v>
@@ -7595,28 +7595,28 @@
         <v>3.6675</v>
       </c>
       <c r="M77">
-        <v>13.033845</v>
+        <v>13.2076296</v>
       </c>
       <c r="N77">
-        <v>-9.366344999999999</v>
+        <v>-9.5401296</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-9.366344999999999</v>
+        <v>-9.5401296</v>
       </c>
       <c r="Q77">
-        <v>-8.396345</v>
+        <v>-8.570129600000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.214902977439148</v>
+        <v>0.2219489348324458</v>
       </c>
       <c r="T77">
-        <v>3.296131781495383</v>
+        <v>3.433470605724357</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2813828152782237</v>
+        <v>0.2776804098140365</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.232475744359787</v>
+        <v>0.234375744359787</v>
       </c>
       <c r="C78">
-        <v>-16.27963955528944</v>
+        <v>-17.129811505995</v>
       </c>
       <c r="D78">
-        <v>11.23236044471056</v>
+        <v>11.11918849400499</v>
       </c>
       <c r="E78">
-        <v>30.61199999999999</v>
+        <v>31.349</v>
       </c>
       <c r="F78">
-        <v>56.01199999999999</v>
+        <v>56.749</v>
       </c>
       <c r="G78">
         <v>28.5</v>
@@ -7677,28 +7677,28 @@
         <v>3.6675</v>
       </c>
       <c r="M78">
-        <v>13.2076296</v>
+        <v>13.3814142</v>
       </c>
       <c r="N78">
-        <v>-9.5401296</v>
+        <v>-9.713914200000001</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-9.5401296</v>
+        <v>-9.713914200000001</v>
       </c>
       <c r="Q78">
-        <v>-8.570129600000001</v>
+        <v>-8.743914200000003</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2219489348324458</v>
+        <v>0.2296075841729869</v>
       </c>
       <c r="T78">
-        <v>3.433470605724357</v>
+        <v>3.582751936408024</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2776804098140365</v>
+        <v>0.2740741707255425</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.234375744359787</v>
+        <v>0.236275744359787</v>
       </c>
       <c r="C79">
-        <v>-17.129811505995</v>
+        <v>-17.97772567099599</v>
       </c>
       <c r="D79">
-        <v>11.11918849400499</v>
+        <v>11.008274329004</v>
       </c>
       <c r="E79">
-        <v>31.349</v>
+        <v>32.08599999999999</v>
       </c>
       <c r="F79">
-        <v>56.749</v>
+        <v>57.48599999999999</v>
       </c>
       <c r="G79">
         <v>28.5</v>
@@ -7759,28 +7759,28 @@
         <v>3.6675</v>
       </c>
       <c r="M79">
-        <v>13.3814142</v>
+        <v>13.5551988</v>
       </c>
       <c r="N79">
-        <v>-9.713914200000001</v>
+        <v>-9.887698799999999</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-9.713914200000001</v>
+        <v>-9.887698799999999</v>
       </c>
       <c r="Q79">
-        <v>-8.743914200000003</v>
+        <v>-8.9176988</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2296075841729869</v>
+        <v>0.2379624743626682</v>
       </c>
       <c r="T79">
-        <v>3.582751936408024</v>
+        <v>3.745604297153844</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2740741707255425</v>
+        <v>0.2705603993059843</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.236275744359787</v>
+        <v>0.238175744359787</v>
       </c>
       <c r="C80">
-        <v>-17.97772567099599</v>
+        <v>-18.8234489473878</v>
       </c>
       <c r="D80">
-        <v>11.008274329004</v>
+        <v>10.8995510526122</v>
       </c>
       <c r="E80">
-        <v>32.08599999999999</v>
+        <v>32.82299999999999</v>
       </c>
       <c r="F80">
-        <v>57.48599999999999</v>
+        <v>58.22299999999999</v>
       </c>
       <c r="G80">
         <v>28.5</v>
@@ -7841,28 +7841,28 @@
         <v>3.6675</v>
       </c>
       <c r="M80">
-        <v>13.5551988</v>
+        <v>13.7289834</v>
       </c>
       <c r="N80">
-        <v>-9.887698799999999</v>
+        <v>-10.0614834</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-9.887698799999999</v>
+        <v>-10.0614834</v>
       </c>
       <c r="Q80">
-        <v>-8.9176988</v>
+        <v>-9.091483400000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2379624743626682</v>
+        <v>0.2471130683799381</v>
       </c>
       <c r="T80">
-        <v>3.745604297153844</v>
+        <v>3.923966406542123</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2705603993059843</v>
+        <v>0.2671355841248959</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.238175744359787</v>
+        <v>0.240075744359787</v>
       </c>
       <c r="C81">
-        <v>-18.8234489473878</v>
+        <v>-19.6670456152745</v>
       </c>
       <c r="D81">
-        <v>10.8995510526122</v>
+        <v>10.79295438472549</v>
       </c>
       <c r="E81">
-        <v>32.82299999999999</v>
+        <v>33.56</v>
       </c>
       <c r="F81">
-        <v>58.22299999999999</v>
+        <v>58.95999999999999</v>
       </c>
       <c r="G81">
         <v>28.5</v>
@@ -7923,28 +7923,28 @@
         <v>3.6675</v>
       </c>
       <c r="M81">
-        <v>13.7289834</v>
+        <v>13.902768</v>
       </c>
       <c r="N81">
-        <v>-10.0614834</v>
+        <v>-10.235268</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-10.0614834</v>
+        <v>-10.235268</v>
       </c>
       <c r="Q81">
-        <v>-9.091483400000001</v>
+        <v>-9.265267999999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2471130683799381</v>
+        <v>0.257178721798935</v>
       </c>
       <c r="T81">
-        <v>3.923966406542123</v>
+        <v>4.120164726869229</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2671355841248959</v>
+        <v>0.2637963893233348</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.240075744359787</v>
+        <v>0.241975744359787</v>
       </c>
       <c r="C82">
-        <v>-19.6670456152745</v>
+        <v>-20.5085774644993</v>
       </c>
       <c r="D82">
-        <v>10.79295438472549</v>
+        <v>10.6884225355007</v>
       </c>
       <c r="E82">
-        <v>33.56</v>
+        <v>34.297</v>
       </c>
       <c r="F82">
-        <v>58.95999999999999</v>
+        <v>59.697</v>
       </c>
       <c r="G82">
         <v>28.5</v>
@@ -8005,28 +8005,28 @@
         <v>3.6675</v>
       </c>
       <c r="M82">
-        <v>13.902768</v>
+        <v>14.0765526</v>
       </c>
       <c r="N82">
-        <v>-10.235268</v>
+        <v>-10.4090526</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-10.235268</v>
+        <v>-10.4090526</v>
       </c>
       <c r="Q82">
-        <v>-9.265267999999999</v>
+        <v>-9.4390526</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.257178721798935</v>
+        <v>0.2683039176830895</v>
       </c>
       <c r="T82">
-        <v>4.120164726869229</v>
+        <v>4.33701550196761</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2637963893233348</v>
+        <v>0.2605396437761331</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.241975744359787</v>
+        <v>0.243875744359787</v>
       </c>
       <c r="C83">
-        <v>-20.5085774644993</v>
+        <v>-21.34810391408095</v>
       </c>
       <c r="D83">
-        <v>10.6884225355007</v>
+        <v>10.58589608591904</v>
       </c>
       <c r="E83">
-        <v>34.297</v>
+        <v>35.034</v>
       </c>
       <c r="F83">
-        <v>59.697</v>
+        <v>60.434</v>
       </c>
       <c r="G83">
         <v>28.5</v>
@@ -8087,28 +8087,28 @@
         <v>3.6675</v>
       </c>
       <c r="M83">
-        <v>14.0765526</v>
+        <v>14.2503372</v>
       </c>
       <c r="N83">
-        <v>-10.4090526</v>
+        <v>-10.5828372</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-10.4090526</v>
+        <v>-10.5828372</v>
       </c>
       <c r="Q83">
-        <v>-9.4390526</v>
+        <v>-9.612837200000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2683039176830895</v>
+        <v>0.2806652464432611</v>
       </c>
       <c r="T83">
-        <v>4.33701550196761</v>
+        <v>4.577960807632477</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2605396437761331</v>
+        <v>0.2573623310471559</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.243875744359787</v>
+        <v>0.245775744359787</v>
       </c>
       <c r="C84">
-        <v>-21.34810391408095</v>
+        <v>-22.18568212484164</v>
       </c>
       <c r="D84">
-        <v>10.58589608591904</v>
+        <v>10.48531787515835</v>
       </c>
       <c r="E84">
-        <v>35.034</v>
+        <v>35.77099999999999</v>
       </c>
       <c r="F84">
-        <v>60.434</v>
+        <v>61.17099999999999</v>
       </c>
       <c r="G84">
         <v>28.5</v>
@@ -8169,28 +8169,28 @@
         <v>3.6675</v>
       </c>
       <c r="M84">
-        <v>14.2503372</v>
+        <v>14.4241218</v>
       </c>
       <c r="N84">
-        <v>-10.5828372</v>
+        <v>-10.7566218</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-10.5828372</v>
+        <v>-10.7566218</v>
       </c>
       <c r="Q84">
-        <v>-9.612837200000001</v>
+        <v>-9.786621799999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2806652464432611</v>
+        <v>0.2944808491752177</v>
       </c>
       <c r="T84">
-        <v>4.577960807632477</v>
+        <v>4.847252619846152</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2573623310471559</v>
+        <v>0.2542615800706841</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.245775744359787</v>
+        <v>0.247675744359787</v>
       </c>
       <c r="C85">
-        <v>-22.18568212484164</v>
+        <v>-23.02136710567468</v>
       </c>
       <c r="D85">
-        <v>10.48531787515835</v>
+        <v>10.38663289432531</v>
       </c>
       <c r="E85">
-        <v>35.77099999999999</v>
+        <v>36.508</v>
       </c>
       <c r="F85">
-        <v>61.17099999999999</v>
+        <v>61.90799999999999</v>
       </c>
       <c r="G85">
         <v>28.5</v>
@@ -8251,28 +8251,28 @@
         <v>3.6675</v>
       </c>
       <c r="M85">
-        <v>14.4241218</v>
+        <v>14.5979064</v>
       </c>
       <c r="N85">
-        <v>-10.7566218</v>
+        <v>-10.9304064</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-10.7566218</v>
+        <v>-10.9304064</v>
       </c>
       <c r="Q85">
-        <v>-9.786621799999999</v>
+        <v>-9.9604064</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2944808491752177</v>
+        <v>0.3100234022486689</v>
       </c>
       <c r="T85">
-        <v>4.847252619846152</v>
+        <v>5.150205908586538</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2542615800706841</v>
+        <v>0.251234656498414</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.247675744359787</v>
+        <v>0.249575744359787</v>
       </c>
       <c r="C86">
-        <v>-23.02136710567468</v>
+        <v>-23.85521181386711</v>
       </c>
       <c r="D86">
-        <v>10.38663289432531</v>
+        <v>10.28978818613288</v>
       </c>
       <c r="E86">
-        <v>36.50799999999999</v>
+        <v>37.24499999999999</v>
       </c>
       <c r="F86">
-        <v>61.90799999999999</v>
+        <v>62.64499999999999</v>
       </c>
       <c r="G86">
         <v>28.5</v>
@@ -8333,28 +8333,28 @@
         <v>3.6675</v>
       </c>
       <c r="M86">
-        <v>14.5979064</v>
+        <v>14.771691</v>
       </c>
       <c r="N86">
-        <v>-10.9304064</v>
+        <v>-11.104191</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-10.9304064</v>
+        <v>-11.104191</v>
       </c>
       <c r="Q86">
-        <v>-9.9604064</v>
+        <v>-10.134191</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3100234022486686</v>
+        <v>0.3276382957319132</v>
       </c>
       <c r="T86">
-        <v>5.150205908586535</v>
+        <v>5.49355296915897</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.251234656498414</v>
+        <v>0.2482789546572561</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.249575744359787</v>
+        <v>0.251475744359787</v>
       </c>
       <c r="C87">
-        <v>-23.85521181386711</v>
+        <v>-24.6872672498618</v>
       </c>
       <c r="D87">
-        <v>10.28978818613288</v>
+        <v>10.1947327501382</v>
       </c>
       <c r="E87">
-        <v>37.24499999999999</v>
+        <v>37.98199999999999</v>
       </c>
       <c r="F87">
-        <v>62.64499999999999</v>
+        <v>63.38199999999999</v>
       </c>
       <c r="G87">
         <v>28.5</v>
@@ -8415,28 +8415,28 @@
         <v>3.6675</v>
       </c>
       <c r="M87">
-        <v>14.771691</v>
+        <v>14.9454756</v>
       </c>
       <c r="N87">
-        <v>-11.104191</v>
+        <v>-11.2779756</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-11.104191</v>
+        <v>-11.2779756</v>
       </c>
       <c r="Q87">
-        <v>-10.134191</v>
+        <v>-10.3079756</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3276382957319132</v>
+        <v>0.347769602569907</v>
       </c>
       <c r="T87">
-        <v>5.49355296915897</v>
+        <v>5.885949609813182</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2482789546572561</v>
+        <v>0.2453919900682184</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.251475744359787</v>
+        <v>0.253375744359787</v>
       </c>
       <c r="C88">
-        <v>-24.6872672498618</v>
+        <v>-25.51758254681522</v>
       </c>
       <c r="D88">
-        <v>10.1947327501382</v>
+        <v>10.10141745318477</v>
       </c>
       <c r="E88">
-        <v>37.98199999999999</v>
+        <v>38.71899999999999</v>
       </c>
       <c r="F88">
-        <v>63.38199999999999</v>
+        <v>64.11899999999999</v>
       </c>
       <c r="G88">
         <v>28.5</v>
@@ -8497,28 +8497,28 @@
         <v>3.6675</v>
       </c>
       <c r="M88">
-        <v>14.9454756</v>
+        <v>15.1192602</v>
       </c>
       <c r="N88">
-        <v>-11.2779756</v>
+        <v>-11.4517602</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-11.2779756</v>
+        <v>-11.4517602</v>
       </c>
       <c r="Q88">
-        <v>-10.3079756</v>
+        <v>-10.4817602</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.347769602569907</v>
+        <v>0.370998033536823</v>
       </c>
       <c r="T88">
-        <v>5.885949609813182</v>
+        <v>6.338714964414197</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2453919900682184</v>
+        <v>0.2425713924812273</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.253375744359787</v>
+        <v>0.255275744359787</v>
       </c>
       <c r="C89">
-        <v>-25.51758254681522</v>
+        <v>-26.34620505528135</v>
       </c>
       <c r="D89">
-        <v>10.10141745318477</v>
+        <v>10.00979494471865</v>
       </c>
       <c r="E89">
-        <v>38.71899999999999</v>
+        <v>39.456</v>
       </c>
       <c r="F89">
-        <v>64.11899999999999</v>
+        <v>64.85599999999999</v>
       </c>
       <c r="G89">
         <v>28.5</v>
@@ -8579,28 +8579,28 @@
         <v>3.6675</v>
       </c>
       <c r="M89">
-        <v>15.1192602</v>
+        <v>15.2930448</v>
       </c>
       <c r="N89">
-        <v>-11.4517602</v>
+        <v>-11.6255448</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-11.4517602</v>
+        <v>-11.6255448</v>
       </c>
       <c r="Q89">
-        <v>-10.4817602</v>
+        <v>-10.6555448</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.370998033536823</v>
+        <v>0.3980978696648916</v>
       </c>
       <c r="T89">
-        <v>6.338714964414197</v>
+        <v>6.866941211448714</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2425713924812273</v>
+        <v>0.2398148993848497</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.255275744359787</v>
+        <v>0.257175744359787</v>
       </c>
       <c r="C90">
-        <v>-26.34620505528135</v>
+        <v>-27.17318042332828</v>
       </c>
       <c r="D90">
-        <v>10.00979494471865</v>
+        <v>9.919819576671715</v>
       </c>
       <c r="E90">
-        <v>39.456</v>
+        <v>40.19299999999999</v>
       </c>
       <c r="F90">
-        <v>64.85599999999999</v>
+        <v>65.59299999999999</v>
       </c>
       <c r="G90">
         <v>28.5</v>
@@ -8661,28 +8661,28 @@
         <v>3.6675</v>
       </c>
       <c r="M90">
-        <v>15.2930448</v>
+        <v>15.4668294</v>
       </c>
       <c r="N90">
-        <v>-11.6255448</v>
+        <v>-11.7993294</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-11.6255448</v>
+        <v>-11.7993294</v>
       </c>
       <c r="Q90">
-        <v>-10.6555448</v>
+        <v>-10.8293294</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3980978696648916</v>
+        <v>0.4301249487253364</v>
       </c>
       <c r="T90">
-        <v>6.866941211448714</v>
+        <v>7.491208594307689</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2398148993848497</v>
+        <v>0.2371203499535594</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.257175744359787</v>
+        <v>0.259075744359787</v>
       </c>
       <c r="C91">
-        <v>-27.17318042332828</v>
+        <v>-27.9985526723726</v>
       </c>
       <c r="D91">
-        <v>9.919819576671715</v>
+        <v>9.831447327627394</v>
       </c>
       <c r="E91">
-        <v>40.19299999999999</v>
+        <v>40.93</v>
       </c>
       <c r="F91">
-        <v>65.59299999999999</v>
+        <v>66.33</v>
       </c>
       <c r="G91">
         <v>28.5</v>
@@ -8743,28 +8743,28 @@
         <v>3.6675</v>
       </c>
       <c r="M91">
-        <v>15.4668294</v>
+        <v>15.640614</v>
       </c>
       <c r="N91">
-        <v>-11.7993294</v>
+        <v>-11.973114</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-11.7993294</v>
+        <v>-11.973114</v>
       </c>
       <c r="Q91">
-        <v>-10.8293294</v>
+        <v>-11.003114</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4301249487253364</v>
+        <v>0.46855744359787</v>
       </c>
       <c r="T91">
-        <v>7.491208594307689</v>
+        <v>8.240329453738457</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2371203499535594</v>
+        <v>0.2344856793985198</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.259075744359787</v>
+        <v>0.260975744359787</v>
       </c>
       <c r="C92">
-        <v>-27.9985526723726</v>
+        <v>-28.82236426899595</v>
       </c>
       <c r="D92">
-        <v>9.831447327627394</v>
+        <v>9.744635731004042</v>
       </c>
       <c r="E92">
-        <v>40.93</v>
+        <v>41.66699999999999</v>
       </c>
       <c r="F92">
-        <v>66.33</v>
+        <v>67.06699999999999</v>
       </c>
       <c r="G92">
         <v>28.5</v>
@@ -8825,28 +8825,28 @@
         <v>3.6675</v>
       </c>
       <c r="M92">
-        <v>15.640614</v>
+        <v>15.8143986</v>
       </c>
       <c r="N92">
-        <v>-11.973114</v>
+        <v>-12.1468986</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-11.973114</v>
+        <v>-12.1468986</v>
       </c>
       <c r="Q92">
-        <v>-11.003114</v>
+        <v>-11.1768986</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.46855744359787</v>
+        <v>0.5155304928865223</v>
       </c>
       <c r="T92">
-        <v>8.240329453738457</v>
+        <v>9.155921615264955</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2344856793985198</v>
+        <v>0.2319089136908437</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.260975744359787</v>
+        <v>0.262875744359787</v>
       </c>
       <c r="C93">
-        <v>-28.82236426899595</v>
+        <v>-29.6446561929901</v>
       </c>
       <c r="D93">
-        <v>9.744635731004042</v>
+        <v>9.659343807009893</v>
       </c>
       <c r="E93">
-        <v>41.66699999999999</v>
+        <v>42.40399999999999</v>
       </c>
       <c r="F93">
-        <v>67.06699999999999</v>
+        <v>67.80399999999999</v>
       </c>
       <c r="G93">
         <v>28.5</v>
@@ -8907,28 +8907,28 @@
         <v>3.6675</v>
       </c>
       <c r="M93">
-        <v>15.8143986</v>
+        <v>15.9881832</v>
       </c>
       <c r="N93">
-        <v>-12.1468986</v>
+        <v>-12.3206832</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-12.1468986</v>
+        <v>-12.3206832</v>
       </c>
       <c r="Q93">
-        <v>-11.1768986</v>
+        <v>-11.3506832</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5155304928865223</v>
+        <v>0.5742468044973377</v>
       </c>
       <c r="T93">
-        <v>9.155921615264955</v>
+        <v>10.30041181717308</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2319089136908437</v>
+        <v>0.2293881646289868</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.262875744359787</v>
+        <v>0.264775744359787</v>
       </c>
       <c r="C94">
-        <v>-29.6446561929901</v>
+        <v>-30.46546800185951</v>
       </c>
       <c r="D94">
-        <v>9.659343807009893</v>
+        <v>9.575531998140484</v>
       </c>
       <c r="E94">
-        <v>42.40399999999999</v>
+        <v>43.141</v>
       </c>
       <c r="F94">
-        <v>67.80399999999999</v>
+        <v>68.541</v>
       </c>
       <c r="G94">
         <v>28.5</v>
@@ -8989,28 +8989,28 @@
         <v>3.6675</v>
       </c>
       <c r="M94">
-        <v>15.9881832</v>
+        <v>16.1619678</v>
       </c>
       <c r="N94">
-        <v>-12.3206832</v>
+        <v>-12.4944678</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-12.3206832</v>
+        <v>-12.4944678</v>
       </c>
       <c r="Q94">
-        <v>-11.3506832</v>
+        <v>-11.5244678</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5742468044973377</v>
+        <v>0.6497392051398144</v>
       </c>
       <c r="T94">
-        <v>10.30041181717308</v>
+        <v>11.77189921962637</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2293881646289868</v>
+        <v>0.226921625224374</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.264775744359787</v>
+        <v>0.266675744359787</v>
       </c>
       <c r="C95">
-        <v>-30.46546800185951</v>
+        <v>-31.2848378919948</v>
       </c>
       <c r="D95">
-        <v>9.575531998140484</v>
+        <v>9.493162108005192</v>
       </c>
       <c r="E95">
-        <v>43.141</v>
+        <v>43.87799999999999</v>
       </c>
       <c r="F95">
-        <v>68.541</v>
+        <v>69.27799999999999</v>
       </c>
       <c r="G95">
         <v>28.5</v>
@@ -9071,28 +9071,28 @@
         <v>3.6675</v>
       </c>
       <c r="M95">
-        <v>16.1619678</v>
+        <v>16.3357524</v>
       </c>
       <c r="N95">
-        <v>-12.4944678</v>
+        <v>-12.6682524</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-12.4944678</v>
+        <v>-12.6682524</v>
       </c>
       <c r="Q95">
-        <v>-11.5244678</v>
+        <v>-11.6982524</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6497392051398144</v>
+        <v>0.7503957393297838</v>
       </c>
       <c r="T95">
-        <v>11.77189921962637</v>
+        <v>13.73388242289744</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.226921625224374</v>
+        <v>0.2245075653815616</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.266675744359787</v>
+        <v>0.268575744359787</v>
       </c>
       <c r="C96">
-        <v>-31.2848378919948</v>
+        <v>-32.1028027567158</v>
       </c>
       <c r="D96">
-        <v>9.493162108005192</v>
+        <v>9.412197243284197</v>
       </c>
       <c r="E96">
-        <v>43.87799999999999</v>
+        <v>44.615</v>
       </c>
       <c r="F96">
-        <v>69.27799999999999</v>
+        <v>70.015</v>
       </c>
       <c r="G96">
         <v>28.5</v>
@@ -9153,28 +9153,28 @@
         <v>3.6675</v>
       </c>
       <c r="M96">
-        <v>16.3357524</v>
+        <v>16.509537</v>
       </c>
       <c r="N96">
-        <v>-12.6682524</v>
+        <v>-12.842037</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-12.6682524</v>
+        <v>-12.842037</v>
       </c>
       <c r="Q96">
-        <v>-11.6982524</v>
+        <v>-11.872037</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7503957393297838</v>
+        <v>0.8913148871957409</v>
       </c>
       <c r="T96">
-        <v>13.73388242289744</v>
+        <v>16.48065890747694</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2245075653815616</v>
+        <v>0.2221443278512293</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.268575744359787</v>
+        <v>0.270475744359787</v>
       </c>
       <c r="C97">
-        <v>-32.1028027567158</v>
+        <v>-32.91939824136946</v>
       </c>
       <c r="D97">
-        <v>9.412197243284197</v>
+        <v>9.332601758630531</v>
       </c>
       <c r="E97">
-        <v>44.615</v>
+        <v>45.352</v>
       </c>
       <c r="F97">
-        <v>70.015</v>
+        <v>70.752</v>
       </c>
       <c r="G97">
         <v>28.5</v>
@@ -9235,28 +9235,28 @@
         <v>3.6675</v>
       </c>
       <c r="M97">
-        <v>16.509537</v>
+        <v>16.6833216</v>
       </c>
       <c r="N97">
-        <v>-12.842037</v>
+        <v>-13.0158216</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-12.842037</v>
+        <v>-13.0158216</v>
       </c>
       <c r="Q97">
-        <v>-11.872037</v>
+        <v>-12.0458216</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8913148871957409</v>
+        <v>1.102693608994677</v>
       </c>
       <c r="T97">
-        <v>16.48065890747694</v>
+        <v>20.60082363434618</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2221443278512293</v>
+        <v>0.2198303244361123</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.270475744359787</v>
+        <v>0.272375744359787</v>
       </c>
       <c r="C98">
-        <v>-32.91939824136945</v>
+        <v>-33.73465879565563</v>
       </c>
       <c r="D98">
-        <v>9.332601758630531</v>
+        <v>9.254341204344362</v>
       </c>
       <c r="E98">
-        <v>45.35199999999998</v>
+        <v>46.08899999999999</v>
       </c>
       <c r="F98">
-        <v>70.75199999999998</v>
+        <v>71.48899999999999</v>
       </c>
       <c r="G98">
         <v>28.5</v>
@@ -9317,28 +9317,28 @@
         <v>3.6675</v>
       </c>
       <c r="M98">
-        <v>16.6833216</v>
+        <v>16.8571062</v>
       </c>
       <c r="N98">
-        <v>-13.0158216</v>
+        <v>-13.1896062</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-13.0158216</v>
+        <v>-13.1896062</v>
       </c>
       <c r="Q98">
-        <v>-12.0458216</v>
+        <v>-12.2196062</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.102693608994674</v>
+        <v>1.454991478659565</v>
       </c>
       <c r="T98">
-        <v>20.60082363434612</v>
+        <v>27.46776484579483</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2198303244361124</v>
+        <v>0.2175640324316164</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.272375744359787</v>
+        <v>0.274275744359787</v>
       </c>
       <c r="C99">
-        <v>-33.73465879565563</v>
+        <v>-34.54861772334191</v>
       </c>
       <c r="D99">
-        <v>9.254341204344362</v>
+        <v>9.177382276658083</v>
       </c>
       <c r="E99">
-        <v>46.08899999999999</v>
+        <v>46.82599999999999</v>
       </c>
       <c r="F99">
-        <v>71.48899999999999</v>
+        <v>72.22599999999998</v>
       </c>
       <c r="G99">
         <v>28.5</v>
@@ -9399,28 +9399,28 @@
         <v>3.6675</v>
       </c>
       <c r="M99">
-        <v>16.8571062</v>
+        <v>17.0308908</v>
       </c>
       <c r="N99">
-        <v>-13.1896062</v>
+        <v>-13.3633908</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-13.1896062</v>
+        <v>-13.3633908</v>
       </c>
       <c r="Q99">
-        <v>-12.2196062</v>
+        <v>-12.3933908</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.454991478659565</v>
+        <v>2.159587217989348</v>
       </c>
       <c r="T99">
-        <v>27.46776484579483</v>
+        <v>41.20164726869225</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2175640324316164</v>
+        <v>0.215343991284355</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.274275744359787</v>
+        <v>0.276175744359787</v>
       </c>
       <c r="C100">
-        <v>-34.54861772334191</v>
+        <v>-35.36130722951847</v>
       </c>
       <c r="D100">
-        <v>9.177382276658083</v>
+        <v>9.101692770481518</v>
       </c>
       <c r="E100">
-        <v>46.82599999999999</v>
+        <v>47.563</v>
       </c>
       <c r="F100">
-        <v>72.22599999999998</v>
+        <v>72.96299999999999</v>
       </c>
       <c r="G100">
         <v>28.5</v>
@@ -9481,28 +9481,28 @@
         <v>3.6675</v>
       </c>
       <c r="M100">
-        <v>17.0308908</v>
+        <v>17.2046754</v>
       </c>
       <c r="N100">
-        <v>-13.3633908</v>
+        <v>-13.5371754</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-13.3633908</v>
+        <v>-13.5371754</v>
       </c>
       <c r="Q100">
-        <v>-12.3933908</v>
+        <v>-12.5671754</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.159587217989348</v>
+        <v>4.273374435978695</v>
       </c>
       <c r="T100">
-        <v>41.20164726869225</v>
+        <v>82.4032945373845</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.215343991284355</v>
+        <v>0.2131687994531998</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.276175744359787</v>
-      </c>
-      <c r="C101">
-        <v>-35.36130722951847</v>
-      </c>
-      <c r="D101">
-        <v>9.101692770481518</v>
-      </c>
-      <c r="E101">
-        <v>47.563</v>
-      </c>
-      <c r="F101">
-        <v>72.96299999999999</v>
-      </c>
-      <c r="G101">
-        <v>28.5</v>
-      </c>
-      <c r="H101">
-        <v>48.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.637499999999999</v>
-      </c>
-      <c r="K101">
-        <v>0.9699999999999998</v>
-      </c>
-      <c r="L101">
-        <v>3.6675</v>
-      </c>
-      <c r="M101">
-        <v>17.2046754</v>
-      </c>
-      <c r="N101">
-        <v>-13.5371754</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-13.5371754</v>
-      </c>
-      <c r="Q101">
-        <v>-12.5671754</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.273374435978695</v>
-      </c>
-      <c r="T101">
-        <v>82.4032945373845</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2358</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2131687994531998</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
